--- a/data/leagues/The Goofy Goobers 2026.xlsx
+++ b/data/leagues/The Goofy Goobers 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="99">
   <si>
     <t>Rice Rice Baby</t>
   </si>
@@ -55,10 +55,13 @@
     <t>Delco Football Team</t>
   </si>
   <si>
-    <t>1-0-0</t>
-  </si>
-  <si>
-    <t>0-1-0</t>
+    <t>1-1-0</t>
+  </si>
+  <si>
+    <t>0-2-0</t>
+  </si>
+  <si>
+    <t>2-0-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -118,6 +121,9 @@
     <t>Week_2</t>
   </si>
   <si>
+    <t>Week_3</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -139,6 +145,9 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>Samuel DiPasqua</t>
+  </si>
+  <si>
     <t>Bridget Cashel</t>
   </si>
   <si>
@@ -148,27 +157,24 @@
     <t>Derrick Edmiston</t>
   </si>
   <si>
-    <t>Samuel DiPasqua</t>
+    <t>Stan Yu</t>
+  </si>
+  <si>
+    <t>Andrew Bock</t>
   </si>
   <si>
     <t>Prahlad Singh</t>
   </si>
   <si>
-    <t>Stan Yu</t>
+    <t>Horatio Kneepads</t>
+  </si>
+  <si>
+    <t>Kermelos Woldeyes</t>
   </si>
   <si>
     <t>Anthony Rizzo</t>
   </si>
   <si>
-    <t>Horatio Kneepads</t>
-  </si>
-  <si>
-    <t>Andrew Bock</t>
-  </si>
-  <si>
-    <t>Kermelos Woldeyes</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -193,63 +199,69 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>1-0</t>
-  </si>
-  <si>
-    <t>0-1</t>
-  </si>
-  <si>
-    <t>13.4-0.6</t>
-  </si>
-  <si>
-    <t>9.9-4.0-0.1</t>
-  </si>
-  <si>
-    <t>9.2-4.7-0.1</t>
-  </si>
-  <si>
-    <t>8.9-5.0-0.1</t>
-  </si>
-  <si>
-    <t>7.2-6.7-0.1</t>
-  </si>
-  <si>
-    <t>5.6-8.2-0.1</t>
-  </si>
-  <si>
-    <t>5.3-8.6-0.1</t>
-  </si>
-  <si>
-    <t>4.8-9.1-0.1</t>
+    <t>2-0</t>
+  </si>
+  <si>
+    <t>1-1</t>
+  </si>
+  <si>
+    <t>0-2</t>
+  </si>
+  <si>
+    <t>11.0-3.0-0.1</t>
+  </si>
+  <si>
+    <t>10.8-3.1-0.1</t>
+  </si>
+  <si>
+    <t>9.2-4.7</t>
+  </si>
+  <si>
+    <t>8.0-5.9-0.1</t>
+  </si>
+  <si>
+    <t>6.8-7.1-0.1</t>
+  </si>
+  <si>
+    <t>5.8-8.1-0.2</t>
+  </si>
+  <si>
+    <t>5.9-8.0-0.1</t>
+  </si>
+  <si>
+    <t>5.0-8.8-0.2</t>
+  </si>
+  <si>
+    <t>3.9-10.1-0.1</t>
   </si>
   <si>
     <t>3.1-10.8-0.1</t>
   </si>
   <si>
-    <t>2.0-11.9-0.1</t>
-  </si>
-  <si>
-    <t>14-0</t>
-  </si>
-  <si>
-    <t>10-4</t>
+    <t>11-3</t>
   </si>
   <si>
     <t>9-5</t>
   </si>
   <si>
+    <t>8-6</t>
+  </si>
+  <si>
     <t>7-7</t>
   </si>
   <si>
+    <t>6-8</t>
+  </si>
+  <si>
     <t>5-9</t>
   </si>
   <si>
+    <t>4-10</t>
+  </si>
+  <si>
     <t>3-11</t>
   </si>
   <si>
-    <t>2-12</t>
-  </si>
-  <si>
     <t>Owners</t>
   </si>
   <si>
@@ -259,7 +271,34 @@
     <t>Change From Last Week</t>
   </si>
   <si>
+    <t>↑4</t>
+  </si>
+  <si>
+    <t>↑5</t>
+  </si>
+  <si>
+    <t>↑3</t>
+  </si>
+  <si>
+    <t>↑2</t>
+  </si>
+  <si>
+    <t>↓2</t>
+  </si>
+  <si>
+    <t>↓9</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>↓11</t>
+  </si>
+  <si>
     <t>Week 1</t>
+  </si>
+  <si>
+    <t>Week 2</t>
   </si>
   <si>
     <t>Week</t>
@@ -681,10 +720,10 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
@@ -705,7 +744,7 @@
         <v>10</v>
       </c>
       <c r="K2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -716,10 +755,10 @@
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -786,10 +825,10 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
@@ -804,13 +843,13 @@
         <v>11</v>
       </c>
       <c r="I5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J5" t="s">
         <v>11</v>
       </c>
       <c r="K5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -821,10 +860,10 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
@@ -833,19 +872,19 @@
         <v>11</v>
       </c>
       <c r="G6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H6" t="s">
         <v>11</v>
       </c>
       <c r="I6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J6" t="s">
         <v>10</v>
       </c>
       <c r="K6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -856,31 +895,31 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -891,31 +930,31 @@
         <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -923,34 +962,34 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -961,10 +1000,10 @@
         <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
@@ -996,10 +1035,10 @@
         <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
@@ -1008,19 +1047,19 @@
         <v>11</v>
       </c>
       <c r="G11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1030,30 +1069,56 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:8">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>85</v>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2">
+        <v>-2</v>
+      </c>
+      <c r="F2">
+        <v>-8</v>
+      </c>
+      <c r="G2">
+        <v>6</v>
+      </c>
+      <c r="H2" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1068,13 +1133,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1082,10 +1147,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
@@ -1096,10 +1161,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
@@ -1113,10 +1178,10 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1124,13 +1189,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1138,13 +1203,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1152,13 +1217,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1166,13 +1231,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1180,10 +1245,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C9">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
@@ -1194,13 +1259,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1208,10 +1273,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C11">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="D11" t="s">
         <v>10</v>
@@ -1229,16 +1294,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1246,16 +1311,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1263,16 +1328,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="D3">
-        <v>-0.09999999999999998</v>
+        <v>-0.3</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1280,13 +1345,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="D4">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -1297,16 +1362,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="D5">
-        <v>-0.3</v>
+        <v>-0.8</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1314,16 +1379,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="D6">
-        <v>0.5</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1331,16 +1396,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C7">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="D7">
-        <v>0.4</v>
+        <v>-0.2</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1348,16 +1413,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="D8">
-        <v>-0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1365,16 +1430,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="D9">
-        <v>0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1382,13 +1447,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C10">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="D10">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="E10" t="s">
         <v>11</v>
@@ -1402,10 +1467,10 @@
         <v>3</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
@@ -1423,66 +1488,66 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B2">
-        <v>98.40000000000001</v>
+        <v>37.6</v>
       </c>
       <c r="C2">
-        <v>1.6</v>
+        <v>38.9</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>18.1</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1494,33 +1559,33 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
-        <v>1.1</v>
+        <v>45.4</v>
       </c>
       <c r="C3">
-        <v>56</v>
+        <v>29.5</v>
       </c>
       <c r="D3">
-        <v>23.1</v>
+        <v>18.2</v>
       </c>
       <c r="E3">
-        <v>13.8</v>
+        <v>5.1</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="G3">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="H3">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="I3">
         <v>0.1</v>
@@ -1532,278 +1597,278 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>99.40000000000001</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>13.3</v>
+      </c>
+      <c r="C4">
+        <v>22.8</v>
+      </c>
+      <c r="D4">
+        <v>32.3</v>
+      </c>
+      <c r="E4">
+        <v>17.7</v>
+      </c>
+      <c r="F4">
         <v>7</v>
-      </c>
-      <c r="B4">
-        <v>0.3</v>
-      </c>
-      <c r="C4">
-        <v>22</v>
-      </c>
-      <c r="D4">
-        <v>34.5</v>
-      </c>
-      <c r="E4">
-        <v>26.2</v>
-      </c>
-      <c r="F4">
-        <v>11.9</v>
       </c>
       <c r="G4">
         <v>3.5</v>
       </c>
       <c r="H4">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="I4">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L4">
-        <v>98.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5">
-        <v>0.2</v>
+        <v>2.3</v>
       </c>
       <c r="C5">
-        <v>17.5</v>
+        <v>5.6</v>
       </c>
       <c r="D5">
-        <v>29</v>
+        <v>18.3</v>
       </c>
       <c r="E5">
-        <v>31.9</v>
+        <v>34.1</v>
       </c>
       <c r="F5">
-        <v>14</v>
+        <v>21.8</v>
       </c>
       <c r="G5">
-        <v>5.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H5">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="I5">
-        <v>0.2</v>
+        <v>2.9</v>
       </c>
       <c r="J5">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L5">
-        <v>98.09999999999999</v>
+        <v>91.40000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="C6">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>10.1</v>
+        <v>7.1</v>
       </c>
       <c r="E6">
-        <v>18</v>
+        <v>17.6</v>
       </c>
       <c r="F6">
-        <v>33.4</v>
+        <v>24.3</v>
       </c>
       <c r="G6">
-        <v>20.2</v>
+        <v>19.4</v>
       </c>
       <c r="H6">
-        <v>10.6</v>
+        <v>14.7</v>
       </c>
       <c r="I6">
-        <v>4.4</v>
+        <v>8.6</v>
       </c>
       <c r="J6">
-        <v>0.7</v>
+        <v>4.6</v>
       </c>
       <c r="K6">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="L6">
-        <v>84</v>
+        <v>71.2</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C7">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D7">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="E7">
-        <v>4.8</v>
+        <v>7.3</v>
       </c>
       <c r="F7">
-        <v>14.9</v>
+        <v>18.5</v>
       </c>
       <c r="G7">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="H7">
-        <v>25.5</v>
+        <v>22.1</v>
       </c>
       <c r="I7">
-        <v>21.6</v>
+        <v>14.4</v>
       </c>
       <c r="J7">
-        <v>7.3</v>
+        <v>9.4</v>
       </c>
       <c r="K7">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="L7">
-        <v>44.8</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="C8">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="D8">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="E8">
-        <v>3.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F8">
-        <v>12.6</v>
+        <v>15.5</v>
       </c>
       <c r="G8">
-        <v>23.5</v>
+        <v>21.3</v>
       </c>
       <c r="H8">
-        <v>25.1</v>
+        <v>19.5</v>
       </c>
       <c r="I8">
-        <v>22.1</v>
+        <v>17.2</v>
       </c>
       <c r="J8">
-        <v>9.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K8">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="L8">
-        <v>40.6</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D9">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E9">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="F9">
-        <v>8.699999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="G9">
-        <v>19.2</v>
+        <v>13.9</v>
       </c>
       <c r="H9">
-        <v>25.9</v>
+        <v>22.8</v>
       </c>
       <c r="I9">
-        <v>26.5</v>
+        <v>27.8</v>
       </c>
       <c r="J9">
-        <v>13.2</v>
+        <v>17.4</v>
       </c>
       <c r="K9">
-        <v>4.2</v>
+        <v>7.1</v>
       </c>
       <c r="L9">
-        <v>30.2</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D10">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E10">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="F10">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="G10">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="H10">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="I10">
-        <v>18.6</v>
+        <v>18</v>
       </c>
       <c r="J10">
-        <v>49</v>
+        <v>34.7</v>
       </c>
       <c r="K10">
-        <v>20</v>
+        <v>27.6</v>
       </c>
       <c r="L10">
-        <v>4</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1812,31 +1877,31 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="G11">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="H11">
-        <v>1.3</v>
+        <v>3.9</v>
       </c>
       <c r="I11">
-        <v>6.3</v>
+        <v>10</v>
       </c>
       <c r="J11">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="K11">
-        <v>72.40000000000001</v>
+        <v>58.2</v>
       </c>
       <c r="L11">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
     </row>
   </sheetData>
@@ -1846,125 +1911,158 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>31</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C2">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2">
+        <v>99.90000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="C3">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="D3">
+        <v>99.8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>100</v>
+      </c>
+      <c r="C4">
+        <v>98.2</v>
+      </c>
+      <c r="D4">
+        <v>97.09999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>62.5</v>
+      </c>
+      <c r="C5">
+        <v>93.10000000000001</v>
+      </c>
+      <c r="D5">
+        <v>91.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3">
+      <c r="B6">
         <v>99.8</v>
       </c>
-      <c r="C3">
-        <v>99.59999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4">
-        <v>97.8</v>
-      </c>
-      <c r="C4">
-        <v>98.8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>97.7</v>
-      </c>
-      <c r="C5">
-        <v>98.2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>85</v>
-      </c>
       <c r="C6">
-        <v>84.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>73.7</v>
+      </c>
+      <c r="D6">
+        <v>71.59999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7">
+        <v>38.1</v>
+      </c>
+      <c r="C7">
+        <v>50.1</v>
+      </c>
+      <c r="D7">
+        <v>50.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="C8">
+        <v>50.2</v>
+      </c>
+      <c r="D8">
+        <v>49.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B7">
-        <v>52.7</v>
-      </c>
-      <c r="C7">
-        <v>44.1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8">
-        <v>31.8</v>
-      </c>
-      <c r="C8">
-        <v>38.1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
+      <c r="B9">
+        <v>54.50000000000001</v>
+      </c>
+      <c r="C9">
+        <v>23.4</v>
+      </c>
+      <c r="D9">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10">
+        <v>0.8</v>
+      </c>
+      <c r="C10">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="D10">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B9">
-        <v>29.9</v>
-      </c>
-      <c r="C9">
-        <v>32.3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>4.6</v>
-      </c>
-      <c r="C10">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="B11">
-        <v>0.7000000000000001</v>
+        <v>38</v>
       </c>
       <c r="C11">
-        <v>0.8999999999999999</v>
+        <v>3.1</v>
+      </c>
+      <c r="D11">
+        <v>4.100000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1979,28 +2077,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2008,28 +2106,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D2">
-        <v>103.86</v>
+        <v>100.07</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
       </c>
       <c r="F2">
-        <v>139.39</v>
+        <v>132.31</v>
       </c>
       <c r="G2">
-        <v>0.615</v>
+        <v>0.542</v>
       </c>
       <c r="H2">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="I2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2037,28 +2135,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D3">
-        <v>114.56</v>
+        <v>119.3</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3">
-        <v>133.04</v>
+        <v>132.16</v>
       </c>
       <c r="G3">
-        <v>0.538</v>
+        <v>0.583</v>
       </c>
       <c r="H3">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2066,28 +2164,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D4">
-        <v>89.40000000000001</v>
+        <v>116.52</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>139.34</v>
+        <v>129.5</v>
       </c>
       <c r="G4">
-        <v>0.615</v>
+        <v>0.5</v>
       </c>
       <c r="H4">
         <v>1.2</v>
       </c>
       <c r="I4">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2095,28 +2193,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D5">
-        <v>117.66</v>
+        <v>107.99</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
       </c>
       <c r="F5">
-        <v>135.54</v>
+        <v>134.03</v>
       </c>
       <c r="G5">
-        <v>0.538</v>
+        <v>0.625</v>
       </c>
       <c r="H5">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="I5">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2124,28 +2222,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D6">
-        <v>116.42</v>
+        <v>125.73</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>129.24</v>
+        <v>130.35</v>
       </c>
       <c r="G6">
-        <v>0.538</v>
+        <v>0.583</v>
       </c>
       <c r="H6">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="I6">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2153,28 +2251,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D7">
-        <v>153.56</v>
+        <v>150.79</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F7">
-        <v>130.72</v>
+        <v>123.26</v>
       </c>
       <c r="G7">
-        <v>0.538</v>
+        <v>0.417</v>
       </c>
       <c r="H7">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="I7">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2182,28 +2280,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D8">
-        <v>127.8</v>
+        <v>122.19</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
       </c>
       <c r="F8">
-        <v>122.9</v>
+        <v>127.35</v>
       </c>
       <c r="G8">
-        <v>0.385</v>
+        <v>0.542</v>
       </c>
       <c r="H8">
-        <v>-0.8</v>
+        <v>-1</v>
       </c>
       <c r="I8">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2214,25 +2312,25 @@
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D9">
-        <v>138.46</v>
+        <v>156.89</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F9">
-        <v>122.9</v>
+        <v>120.86</v>
       </c>
       <c r="G9">
-        <v>0.385</v>
+        <v>0.333</v>
       </c>
       <c r="H9">
-        <v>-0.8</v>
+        <v>-1.2</v>
       </c>
       <c r="I9">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2240,28 +2338,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D10">
-        <v>198.86</v>
+        <v>145.71</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F10">
-        <v>120.29</v>
+        <v>124.4</v>
       </c>
       <c r="G10">
-        <v>0.385</v>
+        <v>0.458</v>
       </c>
       <c r="H10">
-        <v>-1.2</v>
+        <v>-1.9</v>
       </c>
       <c r="I10">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2269,28 +2367,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D11">
-        <v>137.54</v>
+        <v>131.74</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11">
-        <v>124.77</v>
+        <v>122.71</v>
       </c>
       <c r="G11">
-        <v>0.462</v>
+        <v>0.417</v>
       </c>
       <c r="H11">
-        <v>-1.4</v>
+        <v>-2.1</v>
       </c>
       <c r="I11">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -2305,321 +2403,321 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>198.86</v>
+        <v>145.71</v>
       </c>
       <c r="E2">
-        <v>198.86</v>
+        <v>291.42</v>
       </c>
       <c r="F2">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>153.56</v>
+        <v>156.89</v>
       </c>
       <c r="E3">
-        <v>153.56</v>
+        <v>313.78</v>
       </c>
       <c r="F3">
-        <v>99.40000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="I3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>138.46</v>
+        <v>150.79</v>
       </c>
       <c r="E4">
-        <v>138.46</v>
+        <v>301.58</v>
       </c>
       <c r="F4">
-        <v>98.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D5">
-        <v>137.54</v>
+        <v>131.74</v>
       </c>
       <c r="E5">
-        <v>137.54</v>
+        <v>263.48</v>
       </c>
       <c r="F5">
-        <v>98.09999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D6">
-        <v>127.8</v>
+        <v>125.73</v>
       </c>
       <c r="E6">
-        <v>127.8</v>
+        <v>251.46</v>
       </c>
       <c r="F6">
-        <v>84</v>
+        <v>71.2</v>
       </c>
       <c r="G6">
-        <v>0.3</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="H6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7">
         <v>0</v>
       </c>
-      <c r="B7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
       <c r="D7">
-        <v>114.56</v>
+        <v>122.19</v>
       </c>
       <c r="E7">
-        <v>114.56</v>
+        <v>244.38</v>
       </c>
       <c r="F7">
-        <v>44.8</v>
+        <v>51.4</v>
       </c>
       <c r="G7">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="H7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D8">
-        <v>116.42</v>
+        <v>119.3</v>
       </c>
       <c r="E8">
-        <v>116.42</v>
+        <v>238.6</v>
       </c>
       <c r="F8">
-        <v>40.6</v>
+        <v>51.2</v>
       </c>
       <c r="G8">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="H8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="I8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D9">
-        <v>117.66</v>
+        <v>116.52</v>
       </c>
       <c r="E9">
-        <v>117.66</v>
+        <v>233.04</v>
       </c>
       <c r="F9">
-        <v>30.2</v>
+        <v>24.9</v>
       </c>
       <c r="G9">
-        <v>4.2</v>
+        <v>7.1</v>
       </c>
       <c r="H9" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="I9" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>103.86</v>
+        <v>107.99</v>
       </c>
       <c r="E10">
-        <v>103.86</v>
+        <v>215.98</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>9.700000000000001</v>
       </c>
       <c r="G10">
-        <v>20</v>
+        <v>27.6</v>
       </c>
       <c r="H10" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I10" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>89.40000000000001</v>
+        <v>100.07</v>
       </c>
       <c r="E11">
-        <v>89.40000000000001</v>
+        <v>200.14</v>
       </c>
       <c r="F11">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="G11">
-        <v>72.39999999999999</v>
+        <v>58.2</v>
       </c>
       <c r="H11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I11" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -2634,19 +2732,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2654,19 +2752,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2677,16 +2775,16 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2694,19 +2792,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2714,19 +2812,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5">
         <v>5</v>
       </c>
-      <c r="C5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
       <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="F5" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2734,19 +2832,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
-      <c r="F6">
-        <v>0</v>
+      <c r="F6" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2754,19 +2852,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2774,19 +2872,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2794,19 +2892,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D9">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2814,19 +2912,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D10">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
       </c>
-      <c r="F10">
-        <v>0</v>
+      <c r="F10" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2834,19 +2932,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D11">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
       </c>
-      <c r="F11">
-        <v>0</v>
+      <c r="F11" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -2856,125 +2954,158 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>91</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>6</v>
+      </c>
+      <c r="D4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>5</v>
+      </c>
+      <c r="D5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="D6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7">
+        <v>-2</v>
+      </c>
+      <c r="D7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>-4</v>
+      </c>
+      <c r="D8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="B9">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="C9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+        <v>-4</v>
+      </c>
+      <c r="D9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B10">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="C10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>-8</v>
+      </c>
+      <c r="D10" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B11">
-        <v>-8</v>
+        <v>1</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>-10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/The Goofy Goobers 2026.xlsx
+++ b/data/leagues/The Goofy Goobers 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="98">
   <si>
     <t>Rice Rice Baby</t>
   </si>
@@ -208,31 +208,28 @@
     <t>0-2</t>
   </si>
   <si>
-    <t>11.0-3.0-0.1</t>
-  </si>
-  <si>
-    <t>10.8-3.1-0.1</t>
-  </si>
-  <si>
-    <t>9.2-4.7</t>
-  </si>
-  <si>
-    <t>8.0-5.9-0.1</t>
-  </si>
-  <si>
-    <t>6.8-7.1-0.1</t>
-  </si>
-  <si>
-    <t>5.8-8.1-0.2</t>
-  </si>
-  <si>
-    <t>5.9-8.0-0.1</t>
-  </si>
-  <si>
-    <t>5.0-8.8-0.2</t>
-  </si>
-  <si>
-    <t>3.9-10.1-0.1</t>
+    <t>10.9-3.0-0.1</t>
+  </si>
+  <si>
+    <t>9.3-4.7</t>
+  </si>
+  <si>
+    <t>8.1-5.8-0.1</t>
+  </si>
+  <si>
+    <t>6.7-7.2-0.1</t>
+  </si>
+  <si>
+    <t>5.9-8.1-0.1</t>
+  </si>
+  <si>
+    <t>5.7-8.1-0.2</t>
+  </si>
+  <si>
+    <t>5.0-8.9-0.2</t>
+  </si>
+  <si>
+    <t>3.9-10.0-0.1</t>
   </si>
   <si>
     <t>3.1-10.8-0.1</t>
@@ -1074,25 +1071,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1529,25 +1526,25 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>37.6</v>
+        <v>35</v>
       </c>
       <c r="C2">
-        <v>38.9</v>
+        <v>40.5</v>
       </c>
       <c r="D2">
-        <v>18.1</v>
+        <v>19.6</v>
       </c>
       <c r="E2">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="F2">
         <v>0.7</v>
       </c>
       <c r="G2">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1559,7 +1556,7 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1567,37 +1564,37 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>45.4</v>
+        <v>47.3</v>
       </c>
       <c r="C3">
-        <v>29.5</v>
+        <v>30.9</v>
       </c>
       <c r="D3">
-        <v>18.2</v>
+        <v>15.1</v>
       </c>
       <c r="E3">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="F3">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="G3">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
         <v>0.1</v>
       </c>
-      <c r="I3">
-        <v>0.1</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1605,37 +1602,37 @@
         <v>1</v>
       </c>
       <c r="B4">
-        <v>13.3</v>
+        <v>14.8</v>
       </c>
       <c r="C4">
-        <v>22.8</v>
+        <v>18.6</v>
       </c>
       <c r="D4">
-        <v>32.3</v>
+        <v>34</v>
       </c>
       <c r="E4">
-        <v>17.7</v>
+        <v>17.9</v>
       </c>
       <c r="F4">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="G4">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J4">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="K4">
         <v>0.1</v>
       </c>
       <c r="L4">
-        <v>96.59999999999999</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1643,37 +1640,37 @@
         <v>6</v>
       </c>
       <c r="B5">
+        <v>1.9</v>
+      </c>
+      <c r="C5">
+        <v>6.7</v>
+      </c>
+      <c r="D5">
+        <v>19.6</v>
+      </c>
+      <c r="E5">
+        <v>38.5</v>
+      </c>
+      <c r="F5">
+        <v>16.9</v>
+      </c>
+      <c r="G5">
+        <v>8.1</v>
+      </c>
+      <c r="H5">
+        <v>5.3</v>
+      </c>
+      <c r="I5">
         <v>2.3</v>
       </c>
-      <c r="C5">
-        <v>5.6</v>
-      </c>
-      <c r="D5">
-        <v>18.3</v>
-      </c>
-      <c r="E5">
-        <v>34.1</v>
-      </c>
-      <c r="F5">
-        <v>21.8</v>
-      </c>
-      <c r="G5">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="H5">
-        <v>4.8</v>
-      </c>
-      <c r="I5">
-        <v>2.9</v>
-      </c>
       <c r="J5">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K5">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="L5">
-        <v>91.40000000000001</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1681,113 +1678,113 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="D6">
-        <v>7.1</v>
+        <v>5.8</v>
       </c>
       <c r="E6">
-        <v>17.6</v>
+        <v>17.8</v>
       </c>
       <c r="F6">
-        <v>24.3</v>
+        <v>25.6</v>
       </c>
       <c r="G6">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="H6">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="I6">
         <v>8.6</v>
       </c>
       <c r="J6">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="K6">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="L6">
-        <v>71.2</v>
+        <v>71.7</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B7">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C7">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="D7">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="E7">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
       <c r="F7">
-        <v>18.5</v>
+        <v>19.1</v>
       </c>
       <c r="G7">
-        <v>23.6</v>
+        <v>20.5</v>
       </c>
       <c r="H7">
-        <v>22.1</v>
+        <v>19.1</v>
       </c>
       <c r="I7">
-        <v>14.4</v>
+        <v>17.5</v>
       </c>
       <c r="J7">
         <v>9.4</v>
       </c>
       <c r="K7">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="L7">
-        <v>51.4</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B8">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="D8">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="E8">
-        <v>9.800000000000001</v>
+        <v>6.5</v>
       </c>
       <c r="F8">
-        <v>15.5</v>
+        <v>17.4</v>
       </c>
       <c r="G8">
-        <v>21.3</v>
+        <v>23.7</v>
       </c>
       <c r="H8">
-        <v>19.5</v>
+        <v>23.3</v>
       </c>
       <c r="I8">
-        <v>17.2</v>
+        <v>15.1</v>
       </c>
       <c r="J8">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="L8">
-        <v>51.2</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1804,28 +1801,28 @@
         <v>0.5</v>
       </c>
       <c r="E9">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="F9">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G9">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="H9">
-        <v>22.8</v>
+        <v>22</v>
       </c>
       <c r="I9">
-        <v>27.8</v>
+        <v>27.6</v>
       </c>
       <c r="J9">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="K9">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="L9">
-        <v>24.9</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1833,37 +1830,37 @@
         <v>3</v>
       </c>
       <c r="B10">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="G10">
-        <v>5.6</v>
+        <v>6.9</v>
       </c>
       <c r="H10">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="I10">
         <v>18</v>
       </c>
       <c r="J10">
-        <v>34.7</v>
+        <v>36.1</v>
       </c>
       <c r="K10">
-        <v>27.6</v>
+        <v>26.2</v>
       </c>
       <c r="L10">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1877,31 +1874,31 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="F11">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G11">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="H11">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="I11">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="J11">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K11">
-        <v>58.2</v>
+        <v>58.6</v>
       </c>
       <c r="L11">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
     </row>
   </sheetData>
@@ -1930,13 +1927,13 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>99</v>
+        <v>99.2</v>
       </c>
       <c r="C2">
         <v>100</v>
       </c>
       <c r="D2">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1944,13 +1941,13 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>98.09999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="C3">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="D3">
-        <v>99.8</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1961,10 +1958,10 @@
         <v>100</v>
       </c>
       <c r="C4">
-        <v>98.2</v>
+        <v>97.39999999999999</v>
       </c>
       <c r="D4">
-        <v>97.09999999999999</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1972,13 +1969,13 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>62.5</v>
+        <v>65.3</v>
       </c>
       <c r="C5">
-        <v>93.10000000000001</v>
+        <v>94.39999999999999</v>
       </c>
       <c r="D5">
-        <v>91.2</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1986,10 +1983,10 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>99.8</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="C6">
-        <v>73.7</v>
+        <v>72.8</v>
       </c>
       <c r="D6">
         <v>71.59999999999999</v>
@@ -2000,13 +1997,13 @@
         <v>4</v>
       </c>
       <c r="B7">
-        <v>38.1</v>
+        <v>36.7</v>
       </c>
       <c r="C7">
-        <v>50.1</v>
+        <v>54.1</v>
       </c>
       <c r="D7">
-        <v>50.6</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2014,13 +2011,13 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="C8">
-        <v>50.2</v>
+        <v>47.7</v>
       </c>
       <c r="D8">
-        <v>49.2</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2028,13 +2025,13 @@
         <v>0</v>
       </c>
       <c r="B9">
-        <v>54.50000000000001</v>
+        <v>55.7</v>
       </c>
       <c r="C9">
-        <v>23.4</v>
+        <v>22.2</v>
       </c>
       <c r="D9">
-        <v>25.3</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2042,13 +2039,13 @@
         <v>3</v>
       </c>
       <c r="B10">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="C10">
-        <v>8.300000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="D10">
-        <v>11.2</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2056,13 +2053,13 @@
         <v>2</v>
       </c>
       <c r="B11">
-        <v>38</v>
+        <v>36.6</v>
       </c>
       <c r="C11">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="D11">
-        <v>4.100000000000001</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2447,7 +2444,7 @@
         <v>291.42</v>
       </c>
       <c r="F2">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -2456,7 +2453,7 @@
         <v>61</v>
       </c>
       <c r="I2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2476,16 +2473,16 @@
         <v>313.78</v>
       </c>
       <c r="F3">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2505,16 +2502,16 @@
         <v>301.58</v>
       </c>
       <c r="F4">
-        <v>96.59999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="G4">
         <v>0.1</v>
       </c>
       <c r="H4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2534,16 +2531,16 @@
         <v>263.48</v>
       </c>
       <c r="F5">
-        <v>91.40000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="G5">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2563,74 +2560,74 @@
         <v>251.46</v>
       </c>
       <c r="F6">
-        <v>71.2</v>
+        <v>71.7</v>
       </c>
       <c r="G6">
-        <v>0.8999999999999999</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D7">
-        <v>122.19</v>
+        <v>119.3</v>
       </c>
       <c r="E7">
-        <v>244.38</v>
+        <v>238.6</v>
       </c>
       <c r="F7">
-        <v>51.4</v>
+        <v>50.2</v>
       </c>
       <c r="G7">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="H7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C8">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>119.3</v>
+        <v>122.19</v>
       </c>
       <c r="E8">
-        <v>238.6</v>
+        <v>244.38</v>
       </c>
       <c r="F8">
-        <v>51.2</v>
+        <v>50.1</v>
       </c>
       <c r="G8">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="H8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2650,16 +2647,16 @@
         <v>233.04</v>
       </c>
       <c r="F9">
-        <v>24.9</v>
+        <v>25.4</v>
       </c>
       <c r="G9">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="H9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2679,16 +2676,16 @@
         <v>215.98</v>
       </c>
       <c r="F10">
-        <v>9.700000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G10">
-        <v>27.6</v>
+        <v>26.2</v>
       </c>
       <c r="H10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2708,16 +2705,16 @@
         <v>200.14</v>
       </c>
       <c r="F11">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="G11">
-        <v>58.2</v>
+        <v>58.59999999999999</v>
       </c>
       <c r="H11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -2735,16 +2732,16 @@
         <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2764,7 +2761,7 @@
         <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2784,7 +2781,7 @@
         <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2804,7 +2801,7 @@
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2824,7 +2821,7 @@
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2844,7 +2841,7 @@
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2864,7 +2861,7 @@
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2884,7 +2881,7 @@
         <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2904,7 +2901,7 @@
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2924,7 +2921,7 @@
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2944,7 +2941,7 @@
         <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -2959,13 +2956,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>91</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -2979,7 +2976,7 @@
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2993,7 +2990,7 @@
         <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -3007,7 +3004,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3021,7 +3018,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -3035,7 +3032,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -3049,7 +3046,7 @@
         <v>-2</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -3063,7 +3060,7 @@
         <v>-4</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -3077,7 +3074,7 @@
         <v>-4</v>
       </c>
       <c r="D9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -3091,7 +3088,7 @@
         <v>-8</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -3105,7 +3102,7 @@
         <v>-10</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/The Goofy Goobers 2026.xlsx
+++ b/data/leagues/The Goofy Goobers 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="102">
   <si>
     <t>Rice Rice Baby</t>
   </si>
@@ -55,13 +55,16 @@
     <t>Delco Football Team</t>
   </si>
   <si>
-    <t>1-1-0</t>
-  </si>
-  <si>
-    <t>0-2-0</t>
-  </si>
-  <si>
-    <t>2-0-0</t>
+    <t>2-1-0</t>
+  </si>
+  <si>
+    <t>1-2-0</t>
+  </si>
+  <si>
+    <t>3-0-0</t>
+  </si>
+  <si>
+    <t>0-3-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -124,6 +127,9 @@
     <t>Week_3</t>
   </si>
   <si>
+    <t>Week_4</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -145,19 +151,25 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>Marvin Ta</t>
+  </si>
+  <si>
+    <t>Stan Yu</t>
+  </si>
+  <si>
     <t>Samuel DiPasqua</t>
   </si>
   <si>
     <t>Bridget Cashel</t>
   </si>
   <si>
-    <t>Marvin Ta</t>
-  </si>
-  <si>
     <t>Derrick Edmiston</t>
   </si>
   <si>
-    <t>Stan Yu</t>
+    <t>Anthony Rizzo</t>
+  </si>
+  <si>
+    <t>Horatio Kneepads</t>
   </si>
   <si>
     <t>Andrew Bock</t>
@@ -166,15 +178,9 @@
     <t>Prahlad Singh</t>
   </si>
   <si>
-    <t>Horatio Kneepads</t>
-  </si>
-  <si>
     <t>Kermelos Woldeyes</t>
   </si>
   <si>
-    <t>Anthony Rizzo</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -199,51 +205,57 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>2-0</t>
-  </si>
-  <si>
-    <t>1-1</t>
-  </si>
-  <si>
-    <t>0-2</t>
-  </si>
-  <si>
-    <t>10.9-3.0-0.1</t>
-  </si>
-  <si>
-    <t>9.3-4.7</t>
-  </si>
-  <si>
-    <t>8.1-5.8-0.1</t>
-  </si>
-  <si>
-    <t>6.7-7.2-0.1</t>
-  </si>
-  <si>
-    <t>5.9-8.1-0.1</t>
-  </si>
-  <si>
-    <t>5.7-8.1-0.2</t>
-  </si>
-  <si>
-    <t>5.0-8.9-0.2</t>
-  </si>
-  <si>
-    <t>3.9-10.0-0.1</t>
-  </si>
-  <si>
-    <t>3.1-10.8-0.1</t>
-  </si>
-  <si>
-    <t>11-3</t>
+    <t>3-0</t>
+  </si>
+  <si>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>1-2</t>
+  </si>
+  <si>
+    <t>0-3</t>
+  </si>
+  <si>
+    <t>11.8-2.1-0.1</t>
+  </si>
+  <si>
+    <t>9.9-4.0-0.1</t>
+  </si>
+  <si>
+    <t>9.5-4.4-0.1</t>
+  </si>
+  <si>
+    <t>8.7-5.2-0.1</t>
+  </si>
+  <si>
+    <t>6.8-7.1-0.1</t>
+  </si>
+  <si>
+    <t>5.8-8.1-0.1</t>
+  </si>
+  <si>
+    <t>5.6-8.3-0.1</t>
+  </si>
+  <si>
+    <t>5.1-8.8-0.1</t>
+  </si>
+  <si>
+    <t>4.5-9.3-0.1</t>
+  </si>
+  <si>
+    <t>1.7-12.3-0.1</t>
+  </si>
+  <si>
+    <t>12-2</t>
+  </si>
+  <si>
+    <t>10-4</t>
   </si>
   <si>
     <t>9-5</t>
   </si>
   <si>
-    <t>8-6</t>
-  </si>
-  <si>
     <t>7-7</t>
   </si>
   <si>
@@ -256,7 +268,7 @@
     <t>4-10</t>
   </si>
   <si>
-    <t>3-11</t>
+    <t>1-13</t>
   </si>
   <si>
     <t>Owners</t>
@@ -268,34 +280,34 @@
     <t>Change From Last Week</t>
   </si>
   <si>
-    <t>↑4</t>
-  </si>
-  <si>
-    <t>↑5</t>
+    <t>↑6</t>
+  </si>
+  <si>
+    <t>↑8</t>
+  </si>
+  <si>
+    <t>↓3</t>
+  </si>
+  <si>
+    <t>↓1</t>
   </si>
   <si>
     <t>↑3</t>
   </si>
   <si>
-    <t>↑2</t>
-  </si>
-  <si>
-    <t>↓2</t>
+    <t>↓6</t>
   </si>
   <si>
     <t>↓9</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>↓11</t>
-  </si>
-  <si>
     <t>Week 1</t>
   </si>
   <si>
     <t>Week 2</t>
+  </si>
+  <si>
+    <t>Week 3</t>
   </si>
   <si>
     <t>Week</t>
@@ -717,31 +729,31 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
         <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H2" t="s">
         <v>11</v>
       </c>
       <c r="I2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J2" t="s">
         <v>10</v>
       </c>
       <c r="K2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -752,13 +764,13 @@
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
         <v>10</v>
@@ -776,7 +788,7 @@
         <v>10</v>
       </c>
       <c r="K3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -787,31 +799,31 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -846,7 +858,7 @@
         <v>11</v>
       </c>
       <c r="K5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -857,13 +869,13 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F6" t="s">
         <v>11</v>
@@ -881,7 +893,7 @@
         <v>10</v>
       </c>
       <c r="K6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -927,13 +939,13 @@
         <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F8" t="s">
         <v>10</v>
@@ -951,7 +963,7 @@
         <v>12</v>
       </c>
       <c r="K8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -962,31 +974,31 @@
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H9" t="s">
         <v>12</v>
       </c>
       <c r="I9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -994,34 +1006,34 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1032,31 +1044,31 @@
         <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F11" t="s">
         <v>11</v>
       </c>
       <c r="G11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H11" t="s">
         <v>10</v>
       </c>
       <c r="I11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J11" t="s">
         <v>12</v>
       </c>
       <c r="K11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1066,30 +1078,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1116,6 +1128,32 @@
       </c>
       <c r="H2" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1130,13 +1168,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1147,7 +1185,7 @@
         <v>3</v>
       </c>
       <c r="C2">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
@@ -1161,7 +1199,7 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
@@ -1172,13 +1210,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1186,10 +1224,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C5">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
@@ -1200,13 +1238,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1214,13 +1252,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1228,10 +1266,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C8">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
@@ -1242,10 +1280,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
@@ -1256,13 +1294,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1270,13 +1308,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1291,16 +1329,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1311,10 +1349,10 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="D2">
-        <v>-0.3</v>
+        <v>-0.2999999999999998</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
@@ -1325,16 +1363,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1342,13 +1380,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="D4">
-        <v>0.3</v>
+        <v>-0.1000000000000001</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -1359,16 +1397,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C5">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="D5">
-        <v>-0.8</v>
+        <v>-0.1000000000000001</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1376,16 +1414,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="D6">
-        <v>0.1000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1393,16 +1431,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C7">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="D7">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1410,13 +1448,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C8">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="D8">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
@@ -1427,16 +1465,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C9">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="D9">
-        <v>-0.4</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1444,16 +1482,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>0.4</v>
+        <v>-1</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1461,16 +1499,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="D11">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1485,40 +1523,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -1526,22 +1564,22 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>35</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="C2">
-        <v>40.5</v>
+        <v>17.5</v>
       </c>
       <c r="D2">
-        <v>19.6</v>
+        <v>7.3</v>
       </c>
       <c r="E2">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="F2">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="G2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1561,28 +1599,28 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B3">
-        <v>47.3</v>
+        <v>15</v>
       </c>
       <c r="C3">
-        <v>30.9</v>
+        <v>41</v>
       </c>
       <c r="D3">
-        <v>15.1</v>
+        <v>26.8</v>
       </c>
       <c r="E3">
-        <v>4.7</v>
+        <v>11.8</v>
       </c>
       <c r="F3">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1594,45 +1632,45 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>99.90000000000001</v>
+        <v>99.59999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B4">
-        <v>14.8</v>
+        <v>9.4</v>
       </c>
       <c r="C4">
-        <v>18.6</v>
+        <v>27.2</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E4">
-        <v>17.9</v>
+        <v>20.9</v>
       </c>
       <c r="F4">
-        <v>7.5</v>
+        <v>5.4</v>
       </c>
       <c r="G4">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="H4">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="I4">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="J4">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>97.5</v>
+        <v>99.59999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1643,191 +1681,191 @@
         <v>1.9</v>
       </c>
       <c r="C5">
-        <v>6.7</v>
+        <v>12.6</v>
       </c>
       <c r="D5">
-        <v>19.6</v>
+        <v>23.3</v>
       </c>
       <c r="E5">
-        <v>38.5</v>
+        <v>38.9</v>
       </c>
       <c r="F5">
-        <v>16.9</v>
+        <v>14.4</v>
       </c>
       <c r="G5">
-        <v>8.1</v>
+        <v>5.1</v>
       </c>
       <c r="H5">
-        <v>5.3</v>
+        <v>2.7</v>
       </c>
       <c r="I5">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J5">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="K5">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>91.7</v>
+        <v>96.2</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B6">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="C6">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="D6">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="E6">
-        <v>17.8</v>
+        <v>13.9</v>
       </c>
       <c r="F6">
-        <v>25.6</v>
+        <v>32.8</v>
       </c>
       <c r="G6">
-        <v>19.3</v>
+        <v>23.7</v>
       </c>
       <c r="H6">
-        <v>14.8</v>
+        <v>12.2</v>
       </c>
       <c r="I6">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
       <c r="J6">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="K6">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="L6">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
         <v>0.2</v>
       </c>
-      <c r="C7">
-        <v>0.5</v>
-      </c>
       <c r="D7">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="E7">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="F7">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="G7">
-        <v>20.5</v>
+        <v>21.7</v>
       </c>
       <c r="H7">
-        <v>19.1</v>
+        <v>21.4</v>
       </c>
       <c r="I7">
-        <v>17.5</v>
+        <v>17.1</v>
       </c>
       <c r="J7">
-        <v>9.4</v>
+        <v>10.8</v>
       </c>
       <c r="K7">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="L7">
-        <v>50.2</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="1" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
       <c r="C8">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="E8">
-        <v>6.5</v>
+        <v>2.9</v>
       </c>
       <c r="F8">
+        <v>11.6</v>
+      </c>
+      <c r="G8">
+        <v>19.8</v>
+      </c>
+      <c r="H8">
+        <v>22.8</v>
+      </c>
+      <c r="I8">
+        <v>24.6</v>
+      </c>
+      <c r="J8">
         <v>17.4</v>
       </c>
-      <c r="G8">
-        <v>23.7</v>
-      </c>
-      <c r="H8">
-        <v>23.3</v>
-      </c>
-      <c r="I8">
-        <v>15.1</v>
-      </c>
-      <c r="J8">
-        <v>8</v>
-      </c>
       <c r="K8">
-        <v>3.5</v>
+        <v>0.4</v>
       </c>
       <c r="L8">
-        <v>50.1</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B9">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D9">
         <v>0.5</v>
       </c>
       <c r="E9">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="F9">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G9">
-        <v>14</v>
+        <v>17.3</v>
       </c>
       <c r="H9">
-        <v>22</v>
+        <v>22.6</v>
       </c>
       <c r="I9">
-        <v>27.6</v>
+        <v>23.5</v>
       </c>
       <c r="J9">
-        <v>18.1</v>
+        <v>22.5</v>
       </c>
       <c r="K9">
-        <v>6.9</v>
+        <v>2</v>
       </c>
       <c r="L9">
-        <v>25.4</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1839,28 +1877,28 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="F10">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="G10">
-        <v>6.9</v>
+        <v>9.4</v>
       </c>
       <c r="H10">
-        <v>9.9</v>
+        <v>17.4</v>
       </c>
       <c r="I10">
-        <v>18</v>
+        <v>25.2</v>
       </c>
       <c r="J10">
-        <v>36.1</v>
+        <v>39</v>
       </c>
       <c r="K10">
-        <v>26.2</v>
+        <v>3.8</v>
       </c>
       <c r="L10">
-        <v>9.800000000000001</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1877,28 +1915,28 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>2.7</v>
+        <v>0.1</v>
       </c>
       <c r="H11">
-        <v>4.4</v>
+        <v>0.3</v>
       </c>
       <c r="I11">
-        <v>10.3</v>
+        <v>1</v>
       </c>
       <c r="J11">
-        <v>23</v>
+        <v>6.2</v>
       </c>
       <c r="K11">
-        <v>58.6</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="L11">
-        <v>3.7</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -1908,26 +1946,29 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B2">
-        <v>99.2</v>
+        <v>99.3</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -1935,131 +1976,161 @@
       <c r="D2">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>100</v>
+      </c>
+      <c r="C3">
+        <v>99.8</v>
+      </c>
+      <c r="D3">
+        <v>100</v>
+      </c>
+      <c r="E3">
+        <v>99.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3">
+      <c r="B4">
+        <v>96.89999999999999</v>
+      </c>
+      <c r="C4">
+        <v>100</v>
+      </c>
+      <c r="D4">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="E4">
         <v>98.8</v>
       </c>
-      <c r="C3">
-        <v>100</v>
-      </c>
-      <c r="D3">
-        <v>99.7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>100</v>
-      </c>
-      <c r="C4">
-        <v>97.39999999999999</v>
-      </c>
-      <c r="D4">
-        <v>97.2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B5">
-        <v>65.3</v>
+        <v>64.2</v>
       </c>
       <c r="C5">
-        <v>94.39999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="D5">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>98.8</v>
+      </c>
+      <c r="E5">
+        <v>97.09999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>37.8</v>
+      </c>
+      <c r="C6">
+        <v>48.1</v>
+      </c>
+      <c r="D6">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="E6">
+        <v>72.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <v>0.6</v>
+      </c>
+      <c r="C7">
+        <v>3.1</v>
+      </c>
+      <c r="D7">
+        <v>45.3</v>
+      </c>
+      <c r="E7">
+        <v>49.9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8">
+        <v>55.7</v>
+      </c>
+      <c r="C8">
+        <v>32</v>
+      </c>
+      <c r="D8">
+        <v>41.6</v>
+      </c>
+      <c r="E8">
+        <v>37.1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>7.000000000000001</v>
+      </c>
+      <c r="C9">
+        <v>44.4</v>
+      </c>
+      <c r="D9">
+        <v>25.4</v>
+      </c>
+      <c r="E9">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6">
-        <v>99.40000000000001</v>
-      </c>
-      <c r="C6">
-        <v>72.8</v>
-      </c>
-      <c r="D6">
-        <v>71.59999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7">
-        <v>36.7</v>
-      </c>
-      <c r="C7">
-        <v>54.1</v>
-      </c>
-      <c r="D7">
-        <v>51.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>7.8</v>
-      </c>
-      <c r="C8">
-        <v>47.7</v>
-      </c>
-      <c r="D8">
-        <v>46.6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9">
-        <v>55.7</v>
-      </c>
-      <c r="C9">
-        <v>22.2</v>
-      </c>
-      <c r="D9">
-        <v>25.7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="B10">
-        <v>0.5</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="C10">
-        <v>7.6</v>
+        <v>76.8</v>
       </c>
       <c r="D10">
-        <v>10.7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>18.6</v>
+      </c>
+      <c r="E10">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B11">
-        <v>36.6</v>
+        <v>38.6</v>
       </c>
       <c r="C11">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="D11">
-        <v>4</v>
+        <v>0.1</v>
+      </c>
+      <c r="E11">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -2074,28 +2145,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2103,28 +2174,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D2">
-        <v>100.07</v>
+        <v>115.74</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>132.31</v>
+        <v>129.07</v>
       </c>
       <c r="G2">
-        <v>0.542</v>
+        <v>0.515</v>
       </c>
       <c r="H2">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="I2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2132,28 +2203,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D3">
-        <v>119.3</v>
+        <v>114.67</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>132.16</v>
+        <v>131.28</v>
       </c>
       <c r="G3">
-        <v>0.583</v>
+        <v>0.576</v>
       </c>
       <c r="H3">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="I3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2161,28 +2232,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D4">
-        <v>116.52</v>
+        <v>97.83</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F4">
-        <v>129.5</v>
+        <v>130.04</v>
       </c>
       <c r="G4">
-        <v>0.5</v>
+        <v>0.545</v>
       </c>
       <c r="H4">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="I4">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2190,28 +2261,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D5">
-        <v>107.99</v>
+        <v>118.81</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
       </c>
       <c r="F5">
-        <v>134.03</v>
+        <v>129.58</v>
       </c>
       <c r="G5">
-        <v>0.625</v>
+        <v>0.545</v>
       </c>
       <c r="H5">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2219,28 +2290,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D6">
-        <v>125.73</v>
+        <v>122.46</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F6">
-        <v>130.35</v>
+        <v>128.66</v>
       </c>
       <c r="G6">
-        <v>0.583</v>
+        <v>0.545</v>
       </c>
       <c r="H6">
         <v>0.1</v>
       </c>
       <c r="I6">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2248,28 +2319,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D7">
-        <v>150.79</v>
+        <v>133.55</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>123.26</v>
+        <v>124.65</v>
       </c>
       <c r="G7">
-        <v>0.417</v>
+        <v>0.455</v>
       </c>
       <c r="H7">
-        <v>-0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="I7">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2277,28 +2348,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D8">
-        <v>122.19</v>
+        <v>140.85</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F8">
-        <v>127.35</v>
+        <v>122.07</v>
       </c>
       <c r="G8">
-        <v>0.542</v>
+        <v>0.424</v>
       </c>
       <c r="H8">
         <v>-1</v>
       </c>
       <c r="I8">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2306,28 +2377,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D9">
-        <v>156.89</v>
+        <v>147.32</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F9">
-        <v>120.86</v>
+        <v>122.69</v>
       </c>
       <c r="G9">
-        <v>0.333</v>
+        <v>0.455</v>
       </c>
       <c r="H9">
-        <v>-1.2</v>
+        <v>-1.7</v>
       </c>
       <c r="I9">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2335,28 +2406,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D10">
-        <v>145.71</v>
+        <v>124.07</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F10">
-        <v>124.4</v>
+        <v>122.99</v>
       </c>
       <c r="G10">
-        <v>0.458</v>
+        <v>0.485</v>
       </c>
       <c r="H10">
-        <v>-1.9</v>
+        <v>-2.5</v>
       </c>
       <c r="I10">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2364,28 +2435,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D11">
-        <v>131.74</v>
+        <v>148.09</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F11">
-        <v>122.71</v>
+        <v>122.34</v>
       </c>
       <c r="G11">
-        <v>0.417</v>
+        <v>0.455</v>
       </c>
       <c r="H11">
-        <v>-2.1</v>
+        <v>-3.3</v>
       </c>
       <c r="I11">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -2400,31 +2471,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2432,16 +2503,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>145.71</v>
+        <v>148.0933333333333</v>
       </c>
       <c r="E2">
-        <v>291.42</v>
+        <v>444.28</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -2450,68 +2521,68 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D3">
-        <v>156.89</v>
+        <v>147.32</v>
       </c>
       <c r="E3">
-        <v>313.78</v>
+        <v>441.96</v>
       </c>
       <c r="F3">
-        <v>99.90000000000001</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="I3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D4">
-        <v>150.79</v>
+        <v>140.8466666666667</v>
       </c>
       <c r="E4">
-        <v>301.58</v>
+        <v>422.54</v>
       </c>
       <c r="F4">
-        <v>97.5</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="G4">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="I4" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2519,173 +2590,173 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C5">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D5">
-        <v>131.74</v>
+        <v>133.5466666666667</v>
       </c>
       <c r="E5">
-        <v>263.48</v>
+        <v>400.64</v>
       </c>
       <c r="F5">
-        <v>91.7</v>
+        <v>96.2</v>
       </c>
       <c r="G5">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="I5" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D6">
-        <v>125.73</v>
+        <v>124.0666666666667</v>
       </c>
       <c r="E6">
-        <v>251.46</v>
+        <v>372.2</v>
       </c>
       <c r="F6">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="G6">
-        <v>0.7000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="H6" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="I6" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D7">
-        <v>119.3</v>
+        <v>122.46</v>
       </c>
       <c r="E7">
-        <v>238.6</v>
+        <v>367.38</v>
       </c>
       <c r="F7">
-        <v>50.2</v>
+        <v>49.5</v>
       </c>
       <c r="G7">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="H7" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I7" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D8">
-        <v>122.19</v>
+        <v>115.74</v>
       </c>
       <c r="E8">
-        <v>244.38</v>
+        <v>347.22</v>
       </c>
       <c r="F8">
-        <v>50.1</v>
+        <v>34.8</v>
       </c>
       <c r="G8">
-        <v>3.5</v>
+        <v>0.4</v>
       </c>
       <c r="H8" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I8" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C9">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D9">
-        <v>116.52</v>
+        <v>118.8133333333333</v>
       </c>
       <c r="E9">
-        <v>233.04</v>
+        <v>356.4400000000001</v>
       </c>
       <c r="F9">
-        <v>25.4</v>
+        <v>29.4</v>
       </c>
       <c r="G9">
-        <v>6.9</v>
+        <v>2</v>
       </c>
       <c r="H9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="I9" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D10">
-        <v>107.99</v>
+        <v>114.6666666666667</v>
       </c>
       <c r="E10">
-        <v>215.98</v>
+        <v>344</v>
       </c>
       <c r="F10">
-        <v>9.800000000000001</v>
+        <v>14.6</v>
       </c>
       <c r="G10">
-        <v>26.2</v>
+        <v>3.8</v>
       </c>
       <c r="H10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="I10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2693,28 +2764,28 @@
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>100.07</v>
+        <v>97.82666666666667</v>
       </c>
       <c r="E11">
-        <v>200.14</v>
+        <v>293.48</v>
       </c>
       <c r="F11">
-        <v>3.7</v>
+        <v>0.1</v>
       </c>
       <c r="G11">
-        <v>58.59999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="H11" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I11" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -2729,19 +2800,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2752,16 +2823,16 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2769,19 +2840,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D3">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2789,19 +2860,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2809,19 +2880,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D5">
         <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2829,19 +2900,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2849,13 +2920,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D7">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -2869,19 +2940,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C8" t="s">
         <v>45</v>
       </c>
       <c r="D8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2895,13 +2966,13 @@
         <v>42</v>
       </c>
       <c r="D9">
-        <v>-4</v>
+        <v>-10</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2909,19 +2980,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D10">
-        <v>-8</v>
+        <v>-11</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2932,16 +3003,16 @@
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D11">
-        <v>-10</v>
+        <v>-13</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -2951,21 +3022,24 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>94</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -2975,95 +3049,116 @@
       <c r="C2">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="D2">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>-2</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3">
+      <c r="B4">
         <v>4</v>
       </c>
-      <c r="C3">
+      <c r="C4">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
+      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4">
+      <c r="B5">
         <v>1</v>
       </c>
-      <c r="C4">
+      <c r="C5">
         <v>6</v>
       </c>
-      <c r="D4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B6">
         <v>2</v>
       </c>
-      <c r="C5">
+      <c r="C6">
         <v>5</v>
       </c>
-      <c r="D5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6">
-        <v>-2</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>-2</v>
-      </c>
-      <c r="D7" t="s">
+        <v>-4</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>-8</v>
       </c>
       <c r="C8">
-        <v>-4</v>
-      </c>
-      <c r="D8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>-8</v>
+      </c>
+      <c r="D8">
+        <v>-5</v>
+      </c>
+      <c r="E8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
@@ -3073,25 +3168,31 @@
       <c r="C9">
         <v>-4</v>
       </c>
-      <c r="D9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="D9">
+        <v>-10</v>
+      </c>
+      <c r="E9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>-8</v>
-      </c>
-      <c r="D10" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>-2</v>
+      </c>
+      <c r="D10">
+        <v>-11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
         <v>2</v>
       </c>
@@ -3101,8 +3202,11 @@
       <c r="C11">
         <v>-10</v>
       </c>
-      <c r="D11" t="s">
-        <v>88</v>
+      <c r="D11">
+        <v>-13</v>
+      </c>
+      <c r="E11" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/The Goofy Goobers 2026.xlsx
+++ b/data/leagues/The Goofy Goobers 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="105">
   <si>
     <t>Rice Rice Baby</t>
   </si>
@@ -55,16 +55,19 @@
     <t>Delco Football Team</t>
   </si>
   <si>
-    <t>2-1-0</t>
-  </si>
-  <si>
-    <t>1-2-0</t>
-  </si>
-  <si>
-    <t>3-0-0</t>
-  </si>
-  <si>
-    <t>0-3-0</t>
+    <t>3-1-0</t>
+  </si>
+  <si>
+    <t>2-2-0</t>
+  </si>
+  <si>
+    <t>4-0-0</t>
+  </si>
+  <si>
+    <t>1-3-0</t>
+  </si>
+  <si>
+    <t>0-4-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -130,6 +133,9 @@
     <t>Week_4</t>
   </si>
   <si>
+    <t>Week_5</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -154,27 +160,27 @@
     <t>Marvin Ta</t>
   </si>
   <si>
+    <t>Samuel DiPasqua</t>
+  </si>
+  <si>
+    <t>Bridget Cashel</t>
+  </si>
+  <si>
     <t>Stan Yu</t>
   </si>
   <si>
-    <t>Samuel DiPasqua</t>
-  </si>
-  <si>
-    <t>Bridget Cashel</t>
+    <t>Horatio Kneepads</t>
   </si>
   <si>
     <t>Derrick Edmiston</t>
   </si>
   <si>
+    <t>Andrew Bock</t>
+  </si>
+  <si>
     <t>Anthony Rizzo</t>
   </si>
   <si>
-    <t>Horatio Kneepads</t>
-  </si>
-  <si>
-    <t>Andrew Bock</t>
-  </si>
-  <si>
     <t>Prahlad Singh</t>
   </si>
   <si>
@@ -205,46 +211,49 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>3-0</t>
-  </si>
-  <si>
-    <t>2-1</t>
-  </si>
-  <si>
-    <t>1-2</t>
-  </si>
-  <si>
-    <t>0-3</t>
-  </si>
-  <si>
-    <t>11.8-2.1-0.1</t>
-  </si>
-  <si>
-    <t>9.9-4.0-0.1</t>
-  </si>
-  <si>
-    <t>9.5-4.4-0.1</t>
-  </si>
-  <si>
-    <t>8.7-5.2-0.1</t>
-  </si>
-  <si>
-    <t>6.8-7.1-0.1</t>
-  </si>
-  <si>
-    <t>5.8-8.1-0.1</t>
-  </si>
-  <si>
-    <t>5.6-8.3-0.1</t>
-  </si>
-  <si>
-    <t>5.1-8.8-0.1</t>
-  </si>
-  <si>
-    <t>4.5-9.3-0.1</t>
-  </si>
-  <si>
-    <t>1.7-12.3-0.1</t>
+    <t>4-0</t>
+  </si>
+  <si>
+    <t>3-1</t>
+  </si>
+  <si>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>1-3</t>
+  </si>
+  <si>
+    <t>0-4</t>
+  </si>
+  <si>
+    <t>12.0-1.9-0.1</t>
+  </si>
+  <si>
+    <t>9.6-4.3-0.1</t>
+  </si>
+  <si>
+    <t>9.8-4.1-0.1</t>
+  </si>
+  <si>
+    <t>8.7-5.3-0.1</t>
+  </si>
+  <si>
+    <t>7.5-6.4-0.1</t>
+  </si>
+  <si>
+    <t>6.2-7.7-0.1</t>
+  </si>
+  <si>
+    <t>5.0-8.9-0.1</t>
+  </si>
+  <si>
+    <t>4.7-9.2-0.1</t>
+  </si>
+  <si>
+    <t>4.5-9.4-0.1</t>
+  </si>
+  <si>
+    <t>1.6-12.3-0.1</t>
   </si>
   <si>
     <t>12-2</t>
@@ -256,7 +265,7 @@
     <t>9-5</t>
   </si>
   <si>
-    <t>7-7</t>
+    <t>8-6</t>
   </si>
   <si>
     <t>6-8</t>
@@ -265,9 +274,6 @@
     <t>5-9</t>
   </si>
   <si>
-    <t>4-10</t>
-  </si>
-  <si>
     <t>1-13</t>
   </si>
   <si>
@@ -280,27 +286,27 @@
     <t>Change From Last Week</t>
   </si>
   <si>
-    <t>↑6</t>
-  </si>
-  <si>
-    <t>↑8</t>
-  </si>
-  <si>
-    <t>↓3</t>
+    <t>↑5</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>↑2</t>
   </si>
   <si>
     <t>↓1</t>
   </si>
   <si>
+    <t>↓4</t>
+  </si>
+  <si>
+    <t>↑1</t>
+  </si>
+  <si>
     <t>↑3</t>
   </si>
   <si>
-    <t>↓6</t>
-  </si>
-  <si>
-    <t>↓9</t>
-  </si>
-  <si>
     <t>Week 1</t>
   </si>
   <si>
@@ -308,6 +314,9 @@
   </si>
   <si>
     <t>Week 3</t>
+  </si>
+  <si>
+    <t>Week 4</t>
   </si>
   <si>
     <t>Week</t>
@@ -735,7 +744,7 @@
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
         <v>11</v>
@@ -750,7 +759,7 @@
         <v>13</v>
       </c>
       <c r="J2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K2" t="s">
         <v>10</v>
@@ -764,16 +773,16 @@
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3" t="s">
         <v>10</v>
@@ -785,10 +794,10 @@
         <v>10</v>
       </c>
       <c r="J3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -799,31 +808,31 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -834,31 +843,31 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I5" t="s">
         <v>10</v>
       </c>
       <c r="J5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -866,34 +875,34 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -960,7 +969,7 @@
         <v>10</v>
       </c>
       <c r="J8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K8" t="s">
         <v>10</v>
@@ -980,10 +989,10 @@
         <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G9" t="s">
         <v>10</v>
@@ -995,7 +1004,7 @@
         <v>10</v>
       </c>
       <c r="J9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K9" t="s">
         <v>10</v>
@@ -1009,19 +1018,19 @@
         <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H10" t="s">
         <v>11</v>
@@ -1030,10 +1039,10 @@
         <v>11</v>
       </c>
       <c r="J10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1047,13 +1056,13 @@
         <v>11</v>
       </c>
       <c r="D11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G11" t="s">
         <v>11</v>
@@ -1065,7 +1074,7 @@
         <v>11</v>
       </c>
       <c r="J11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K11" t="s">
         <v>11</v>
@@ -1078,30 +1087,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1109,25 +1118,25 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E2">
-        <v>-2</v>
+        <v>-11</v>
       </c>
       <c r="F2">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H2" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1135,25 +1144,103 @@
         <v>1</v>
       </c>
       <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3">
+        <v>-2</v>
+      </c>
+      <c r="F3">
+        <v>-8</v>
+      </c>
+      <c r="G3">
+        <v>6</v>
+      </c>
+      <c r="H3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>-4</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+      <c r="H4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
         <v>7</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D5" t="s">
         <v>4</v>
       </c>
-      <c r="E3">
+      <c r="E5">
         <v>5</v>
       </c>
-      <c r="F3">
+      <c r="F5">
         <v>4</v>
       </c>
-      <c r="G3">
+      <c r="G5">
         <v>1</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H5" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1168,13 +1255,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1185,10 +1272,10 @@
         <v>3</v>
       </c>
       <c r="C2">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1199,10 +1286,10 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1210,13 +1297,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1224,13 +1311,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1238,10 +1325,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="D6" t="s">
         <v>13</v>
@@ -1252,13 +1339,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C7">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1266,10 +1353,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
@@ -1280,10 +1367,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C9">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
@@ -1294,10 +1381,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="D10" t="s">
         <v>10</v>
@@ -1308,13 +1395,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="D11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1329,16 +1416,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1349,7 +1436,7 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="D2">
         <v>-0.2999999999999998</v>
@@ -1366,10 +1453,10 @@
         <v>6</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>-0.1000000000000001</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -1380,13 +1467,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C4">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="D4">
-        <v>-0.1000000000000001</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -1397,16 +1484,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="D5">
-        <v>-0.1000000000000001</v>
+        <v>0.2999999999999998</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1414,16 +1501,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="D6">
-        <v>0.3999999999999999</v>
+        <v>-1.2</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1431,13 +1518,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C7">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="D7">
-        <v>0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
@@ -1448,16 +1535,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="D8">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1465,16 +1552,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C9">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="D9">
-        <v>0.1000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1482,16 +1569,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1502,13 +1589,13 @@
         <v>2</v>
       </c>
       <c r="C11">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D11">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1523,40 +1610,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -1564,19 +1651,19 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>73.59999999999999</v>
+        <v>81</v>
       </c>
       <c r="C2">
-        <v>17.5</v>
+        <v>13.2</v>
       </c>
       <c r="D2">
-        <v>7.3</v>
+        <v>4.1</v>
       </c>
       <c r="E2">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="F2">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1599,25 +1686,25 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B3">
-        <v>15</v>
+        <v>7.2</v>
       </c>
       <c r="C3">
-        <v>41</v>
+        <v>29.3</v>
       </c>
       <c r="D3">
-        <v>26.8</v>
+        <v>30.3</v>
       </c>
       <c r="E3">
-        <v>11.8</v>
+        <v>22.6</v>
       </c>
       <c r="F3">
-        <v>3.8</v>
+        <v>8.1</v>
       </c>
       <c r="G3">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="H3">
         <v>0.3</v>
@@ -1626,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>99.59999999999999</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1640,28 +1727,28 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>9.4</v>
+        <v>8.9</v>
       </c>
       <c r="C4">
-        <v>27.2</v>
+        <v>37.5</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E4">
-        <v>20.9</v>
+        <v>15.9</v>
       </c>
       <c r="F4">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="G4">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="H4">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="I4">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1670,197 +1757,197 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>99.59999999999999</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B5">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="C5">
-        <v>12.6</v>
+        <v>16.5</v>
       </c>
       <c r="D5">
-        <v>23.3</v>
+        <v>26.1</v>
       </c>
       <c r="E5">
-        <v>38.9</v>
+        <v>31.7</v>
       </c>
       <c r="F5">
-        <v>14.4</v>
+        <v>13.5</v>
       </c>
       <c r="G5">
-        <v>5.1</v>
+        <v>6.5</v>
       </c>
       <c r="H5">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J5">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>96.2</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B6">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C6">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="D6">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="E6">
-        <v>13.9</v>
+        <v>17.2</v>
       </c>
       <c r="F6">
-        <v>32.8</v>
+        <v>39.3</v>
       </c>
       <c r="G6">
-        <v>23.7</v>
+        <v>21.1</v>
       </c>
       <c r="H6">
-        <v>12.2</v>
+        <v>8</v>
       </c>
       <c r="I6">
-        <v>7.7</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="K6">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>76.2</v>
+        <v>88.09999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="D7">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E7">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="F7">
-        <v>19</v>
+        <v>17.3</v>
       </c>
       <c r="G7">
-        <v>21.7</v>
+        <v>32.5</v>
       </c>
       <c r="H7">
-        <v>21.4</v>
+        <v>24.2</v>
       </c>
       <c r="I7">
-        <v>17.1</v>
+        <v>11</v>
       </c>
       <c r="J7">
-        <v>10.8</v>
+        <v>4.7</v>
       </c>
       <c r="K7">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="L7">
-        <v>49.5</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D8">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E8">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="F8">
-        <v>11.6</v>
+        <v>6.5</v>
       </c>
       <c r="G8">
-        <v>19.8</v>
+        <v>16.3</v>
       </c>
       <c r="H8">
-        <v>22.8</v>
+        <v>26.8</v>
       </c>
       <c r="I8">
-        <v>24.6</v>
+        <v>25.6</v>
       </c>
       <c r="J8">
-        <v>17.4</v>
+        <v>20.2</v>
       </c>
       <c r="K8">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="L8">
-        <v>34.8</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D9">
+        <v>0.3</v>
+      </c>
+      <c r="E9">
         <v>0.5</v>
       </c>
-      <c r="E9">
-        <v>2.6</v>
-      </c>
       <c r="F9">
-        <v>8.800000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="G9">
-        <v>17.3</v>
+        <v>10.3</v>
       </c>
       <c r="H9">
-        <v>22.6</v>
+        <v>19.6</v>
       </c>
       <c r="I9">
-        <v>23.5</v>
+        <v>30.6</v>
       </c>
       <c r="J9">
-        <v>22.5</v>
+        <v>31.3</v>
       </c>
       <c r="K9">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="L9">
-        <v>29.4</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1877,28 +1964,28 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="F10">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="G10">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="H10">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="I10">
-        <v>25.2</v>
+        <v>26.7</v>
       </c>
       <c r="J10">
-        <v>39</v>
+        <v>35.1</v>
       </c>
       <c r="K10">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="L10">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1921,22 +2008,22 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J11">
-        <v>6.2</v>
+        <v>7.7</v>
       </c>
       <c r="K11">
-        <v>92.40000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="L11">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1946,29 +2033,32 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>35</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B2">
-        <v>99.3</v>
+        <v>99.2</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -1979,30 +2069,36 @@
       <c r="E2">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B3">
-        <v>100</v>
+        <v>62.1</v>
       </c>
       <c r="C3">
-        <v>99.8</v>
+        <v>94.39999999999999</v>
       </c>
       <c r="D3">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="E3">
-        <v>99.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="F3">
+        <v>99.59999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B4">
-        <v>96.89999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -2011,95 +2107,113 @@
         <v>99.09999999999999</v>
       </c>
       <c r="E4">
-        <v>98.8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>99.7</v>
+      </c>
+      <c r="F4">
+        <v>99.59999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B5">
-        <v>64.2</v>
+        <v>100</v>
       </c>
       <c r="C5">
-        <v>95.3</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="D5">
-        <v>98.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="E5">
-        <v>97.09999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>98</v>
+      </c>
+      <c r="F5">
+        <v>98.40000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6">
+        <v>57.99999999999999</v>
+      </c>
+      <c r="C6">
+        <v>27.8</v>
+      </c>
+      <c r="D6">
+        <v>40</v>
+      </c>
+      <c r="E6">
+        <v>89.2</v>
+      </c>
+      <c r="F6">
+        <v>88.09999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>7.000000000000001</v>
+      </c>
+      <c r="C7">
+        <v>46.9</v>
+      </c>
+      <c r="D7">
+        <v>24.4</v>
+      </c>
+      <c r="E7">
+        <v>59.59999999999999</v>
+      </c>
+      <c r="F7">
+        <v>59.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>0.5</v>
+      </c>
+      <c r="C8">
+        <v>3.8</v>
+      </c>
+      <c r="D8">
+        <v>47.3</v>
+      </c>
+      <c r="E8">
+        <v>26.3</v>
+      </c>
+      <c r="F8">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6">
-        <v>37.8</v>
-      </c>
-      <c r="C6">
-        <v>48.1</v>
-      </c>
-      <c r="D6">
-        <v>71.09999999999999</v>
-      </c>
-      <c r="E6">
-        <v>72.3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7">
-        <v>0.6</v>
-      </c>
-      <c r="C7">
-        <v>3.1</v>
-      </c>
-      <c r="D7">
-        <v>45.3</v>
-      </c>
-      <c r="E7">
-        <v>49.9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8">
-        <v>55.7</v>
-      </c>
-      <c r="C8">
-        <v>32</v>
-      </c>
-      <c r="D8">
-        <v>41.6</v>
-      </c>
-      <c r="E8">
-        <v>37.1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="B9">
-        <v>7.000000000000001</v>
+        <v>36.6</v>
       </c>
       <c r="C9">
-        <v>44.4</v>
+        <v>48.5</v>
       </c>
       <c r="D9">
-        <v>25.4</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="E9">
-        <v>27.3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>16.2</v>
+      </c>
+      <c r="F9">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -2107,30 +2221,36 @@
         <v>99.90000000000001</v>
       </c>
       <c r="C10">
-        <v>76.8</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="D10">
-        <v>18.6</v>
+        <v>21</v>
       </c>
       <c r="E10">
-        <v>17.8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>11.6</v>
+      </c>
+      <c r="F10">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B11">
-        <v>38.6</v>
+        <v>39.2</v>
       </c>
       <c r="C11">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="D11">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E11">
-        <v>0.2</v>
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2145,28 +2265,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2177,25 +2297,25 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D2">
-        <v>115.74</v>
+        <v>126.56</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2">
-        <v>129.07</v>
+        <v>130.98</v>
       </c>
       <c r="G2">
-        <v>0.515</v>
+        <v>0.525</v>
       </c>
       <c r="H2">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="I2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2203,28 +2323,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D3">
-        <v>114.67</v>
+        <v>95.62</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F3">
-        <v>131.28</v>
+        <v>130.08</v>
       </c>
       <c r="G3">
-        <v>0.576</v>
+        <v>0.525</v>
       </c>
       <c r="H3">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="I3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2232,28 +2352,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D4">
-        <v>97.83</v>
+        <v>123.64</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>130.04</v>
+        <v>130.06</v>
       </c>
       <c r="G4">
-        <v>0.545</v>
+        <v>0.525</v>
       </c>
       <c r="H4">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2261,28 +2381,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D5">
-        <v>118.81</v>
+        <v>116.34</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F5">
-        <v>129.58</v>
+        <v>130.99</v>
       </c>
       <c r="G5">
-        <v>0.545</v>
+        <v>0.525</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I5">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2290,28 +2410,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D6">
-        <v>122.46</v>
+        <v>144.31</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>128.66</v>
+        <v>125.84</v>
       </c>
       <c r="G6">
-        <v>0.545</v>
+        <v>0.45</v>
       </c>
       <c r="H6">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="I6">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2319,28 +2439,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D7">
-        <v>133.55</v>
+        <v>120.63</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F7">
-        <v>124.65</v>
+        <v>130.58</v>
       </c>
       <c r="G7">
-        <v>0.455</v>
+        <v>0.55</v>
       </c>
       <c r="H7">
-        <v>-0.3</v>
+        <v>-0.5</v>
       </c>
       <c r="I7">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2348,28 +2468,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D8">
-        <v>140.85</v>
+        <v>144.16</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F8">
-        <v>122.07</v>
+        <v>125.43</v>
       </c>
       <c r="G8">
-        <v>0.424</v>
+        <v>0.475</v>
       </c>
       <c r="H8">
         <v>-1</v>
       </c>
       <c r="I8">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2377,28 +2497,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D9">
-        <v>147.32</v>
+        <v>142.16</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9">
-        <v>122.69</v>
+        <v>126.36</v>
       </c>
       <c r="G9">
-        <v>0.455</v>
+        <v>0.475</v>
       </c>
       <c r="H9">
-        <v>-1.7</v>
+        <v>-1.2</v>
       </c>
       <c r="I9">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2409,25 +2529,25 @@
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D10">
-        <v>124.07</v>
+        <v>114.38</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F10">
-        <v>122.99</v>
+        <v>126.33</v>
       </c>
       <c r="G10">
-        <v>0.485</v>
+        <v>0.475</v>
       </c>
       <c r="H10">
-        <v>-2.5</v>
+        <v>-1.8</v>
       </c>
       <c r="I10">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2438,25 +2558,25 @@
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D11">
-        <v>148.09</v>
+        <v>154.29</v>
       </c>
       <c r="E11" t="s">
         <v>12</v>
       </c>
       <c r="F11">
-        <v>122.34</v>
+        <v>125.44</v>
       </c>
       <c r="G11">
-        <v>0.455</v>
+        <v>0.475</v>
       </c>
       <c r="H11">
-        <v>-3.3</v>
+        <v>-3.1</v>
       </c>
       <c r="I11">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2471,31 +2591,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2503,16 +2623,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>148.0933333333333</v>
+        <v>154.29</v>
       </c>
       <c r="E2">
-        <v>444.28</v>
+        <v>617.16</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -2521,39 +2641,39 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="I2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C3">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="D3">
-        <v>147.32</v>
+        <v>142.165</v>
       </c>
       <c r="E3">
-        <v>441.96</v>
+        <v>568.66</v>
       </c>
       <c r="F3">
-        <v>99.59999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="I3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2561,173 +2681,173 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C4">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="D4">
-        <v>140.8466666666667</v>
+        <v>144.315</v>
       </c>
       <c r="E4">
-        <v>422.54</v>
+        <v>577.26</v>
       </c>
       <c r="F4">
-        <v>99.59999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C5">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="D5">
-        <v>133.5466666666667</v>
+        <v>144.16</v>
       </c>
       <c r="E5">
-        <v>400.64</v>
+        <v>576.6400000000001</v>
       </c>
       <c r="F5">
-        <v>96.2</v>
+        <v>97</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C6">
-        <v>0.3333333333333333</v>
+        <v>0.75</v>
       </c>
       <c r="D6">
-        <v>124.0666666666667</v>
+        <v>126.56</v>
       </c>
       <c r="E6">
-        <v>372.2</v>
+        <v>506.24</v>
       </c>
       <c r="F6">
-        <v>76.2</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="G6">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="I6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C7">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="D7">
-        <v>122.46</v>
+        <v>123.635</v>
       </c>
       <c r="E7">
-        <v>367.38</v>
+        <v>494.5400000000001</v>
       </c>
       <c r="F7">
-        <v>49.5</v>
+        <v>59.7</v>
       </c>
       <c r="G7">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="H7" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C8">
-        <v>0.6666666666666666</v>
+        <v>0.25</v>
       </c>
       <c r="D8">
-        <v>115.74</v>
+        <v>120.63</v>
       </c>
       <c r="E8">
-        <v>347.22</v>
+        <v>482.52</v>
       </c>
       <c r="F8">
-        <v>34.8</v>
+        <v>25.4</v>
       </c>
       <c r="G8">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="H8" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I8" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C9">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="D9">
-        <v>118.8133333333333</v>
+        <v>114.375</v>
       </c>
       <c r="E9">
-        <v>356.4400000000001</v>
+        <v>457.5</v>
       </c>
       <c r="F9">
-        <v>29.4</v>
+        <v>15.4</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="H9" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I9" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2735,28 +2855,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C10">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="D10">
-        <v>114.6666666666667</v>
+        <v>116.345</v>
       </c>
       <c r="E10">
-        <v>344</v>
+        <v>465.38</v>
       </c>
       <c r="F10">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="G10">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="H10" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2764,28 +2884,28 @@
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>97.82666666666667</v>
+        <v>95.62</v>
       </c>
       <c r="E11">
-        <v>293.48</v>
+        <v>382.48</v>
       </c>
       <c r="F11">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>92.40000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="H11" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I11" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -2800,19 +2920,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2823,16 +2943,16 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2843,16 +2963,16 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D3">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2860,19 +2980,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4">
         <v>7</v>
       </c>
-      <c r="C4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4">
-        <v>5</v>
-      </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2880,19 +3000,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2900,19 +3020,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C6" t="s">
         <v>50</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2920,19 +3040,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F7" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2943,16 +3063,16 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D8">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2960,19 +3080,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D9">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F9" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2980,19 +3100,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D10">
         <v>-11</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3003,16 +3123,16 @@
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D11">
-        <v>-13</v>
+        <v>-17</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F11" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -3022,24 +3142,27 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>97</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -3052,11 +3175,14 @@
       <c r="D2">
         <v>14</v>
       </c>
-      <c r="E2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="E2">
+        <v>19</v>
+      </c>
+      <c r="F2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -3069,79 +3195,94 @@
       <c r="D3">
         <v>8</v>
       </c>
-      <c r="E3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="E3">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D4">
         <v>5</v>
       </c>
-      <c r="E4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="E4">
+        <v>7</v>
+      </c>
+      <c r="F4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D5">
         <v>5</v>
       </c>
-      <c r="E5" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>-4</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6">
+      <c r="B7">
         <v>2</v>
       </c>
-      <c r="C6">
+      <c r="C7">
         <v>5</v>
       </c>
-      <c r="D6">
+      <c r="D7">
         <v>4</v>
       </c>
-      <c r="E6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>-4</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
@@ -3154,45 +3295,54 @@
       <c r="D8">
         <v>-5</v>
       </c>
-      <c r="E8" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="E8">
+        <v>-4</v>
+      </c>
+      <c r="F8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>-2</v>
+      </c>
+      <c r="D9">
+        <v>-11</v>
+      </c>
+      <c r="E9">
+        <v>-8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10">
         <v>-6</v>
       </c>
-      <c r="C9">
+      <c r="C10">
         <v>-4</v>
       </c>
-      <c r="D9">
+      <c r="D10">
         <v>-10</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E10">
+        <v>-11</v>
+      </c>
+      <c r="F10" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>-2</v>
-      </c>
-      <c r="D10">
-        <v>-11</v>
-      </c>
-      <c r="E10" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
         <v>2</v>
       </c>
@@ -3205,8 +3355,11 @@
       <c r="D11">
         <v>-13</v>
       </c>
-      <c r="E11" t="s">
-        <v>87</v>
+      <c r="E11">
+        <v>-17</v>
+      </c>
+      <c r="F11" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/The Goofy Goobers 2026.xlsx
+++ b/data/leagues/The Goofy Goobers 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="109">
   <si>
     <t>Rice Rice Baby</t>
   </si>
@@ -55,19 +55,22 @@
     <t>Delco Football Team</t>
   </si>
   <si>
-    <t>3-1-0</t>
-  </si>
-  <si>
-    <t>2-2-0</t>
-  </si>
-  <si>
-    <t>4-0-0</t>
-  </si>
-  <si>
-    <t>1-3-0</t>
-  </si>
-  <si>
-    <t>0-4-0</t>
+    <t>4-1-0</t>
+  </si>
+  <si>
+    <t>3-2-0</t>
+  </si>
+  <si>
+    <t>2-3-0</t>
+  </si>
+  <si>
+    <t>1-4-0</t>
+  </si>
+  <si>
+    <t>0-5-0</t>
+  </si>
+  <si>
+    <t>5-0-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -136,6 +139,9 @@
     <t>Week_5</t>
   </si>
   <si>
+    <t>Week_6</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -157,33 +163,33 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>Samuel DiPasqua</t>
+  </si>
+  <si>
     <t>Marvin Ta</t>
   </si>
   <si>
-    <t>Samuel DiPasqua</t>
+    <t>Horatio Kneepads</t>
+  </si>
+  <si>
+    <t>Stan Yu</t>
   </si>
   <si>
     <t>Bridget Cashel</t>
   </si>
   <si>
-    <t>Stan Yu</t>
-  </si>
-  <si>
-    <t>Horatio Kneepads</t>
-  </si>
-  <si>
     <t>Derrick Edmiston</t>
   </si>
   <si>
+    <t>Prahlad Singh</t>
+  </si>
+  <si>
+    <t>Anthony Rizzo</t>
+  </si>
+  <si>
     <t>Andrew Bock</t>
   </si>
   <si>
-    <t>Anthony Rizzo</t>
-  </si>
-  <si>
-    <t>Prahlad Singh</t>
-  </si>
-  <si>
     <t>Kermelos Woldeyes</t>
   </si>
   <si>
@@ -211,34 +217,37 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>4-0</t>
-  </si>
-  <si>
-    <t>3-1</t>
-  </si>
-  <si>
-    <t>2-2</t>
-  </si>
-  <si>
-    <t>1-3</t>
-  </si>
-  <si>
-    <t>0-4</t>
-  </si>
-  <si>
-    <t>12.0-1.9-0.1</t>
-  </si>
-  <si>
-    <t>9.6-4.3-0.1</t>
-  </si>
-  <si>
-    <t>9.8-4.1-0.1</t>
-  </si>
-  <si>
-    <t>8.7-5.3-0.1</t>
-  </si>
-  <si>
-    <t>7.5-6.4-0.1</t>
+    <t>4-1</t>
+  </si>
+  <si>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>2-3</t>
+  </si>
+  <si>
+    <t>1-4</t>
+  </si>
+  <si>
+    <t>0-5</t>
+  </si>
+  <si>
+    <t>10.7-3.2-0.1</t>
+  </si>
+  <si>
+    <t>9.1-4.8-0.1</t>
+  </si>
+  <si>
+    <t>9.3-4.7-0.1</t>
+  </si>
+  <si>
+    <t>8.4-5.5-0.1</t>
+  </si>
+  <si>
+    <t>8.6-5.3-0.1</t>
+  </si>
+  <si>
+    <t>7.6-6.4-0.1</t>
   </si>
   <si>
     <t>6.2-7.7-0.1</t>
@@ -247,19 +256,13 @@
     <t>5.0-8.9-0.1</t>
   </si>
   <si>
-    <t>4.7-9.2-0.1</t>
-  </si>
-  <si>
-    <t>4.5-9.4-0.1</t>
-  </si>
-  <si>
-    <t>1.6-12.3-0.1</t>
-  </si>
-  <si>
-    <t>12-2</t>
-  </si>
-  <si>
-    <t>10-4</t>
+    <t>3.6-10.3-0.1</t>
+  </si>
+  <si>
+    <t>1.2-12.8-0.1</t>
+  </si>
+  <si>
+    <t>11-3</t>
   </si>
   <si>
     <t>9-5</t>
@@ -274,6 +277,9 @@
     <t>5-9</t>
   </si>
   <si>
+    <t>3-11</t>
+  </si>
+  <si>
     <t>1-13</t>
   </si>
   <si>
@@ -286,27 +292,30 @@
     <t>Change From Last Week</t>
   </si>
   <si>
-    <t>↑5</t>
+    <t>↓1</t>
+  </si>
+  <si>
+    <t>↑9</t>
+  </si>
+  <si>
+    <t>↑2</t>
+  </si>
+  <si>
+    <t>↓9</t>
+  </si>
+  <si>
+    <t>↑6</t>
+  </si>
+  <si>
+    <t>↓8</t>
+  </si>
+  <si>
+    <t>↑1</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
-    <t>↑2</t>
-  </si>
-  <si>
-    <t>↓1</t>
-  </si>
-  <si>
-    <t>↓4</t>
-  </si>
-  <si>
-    <t>↑1</t>
-  </si>
-  <si>
-    <t>↑3</t>
-  </si>
-  <si>
     <t>Week 1</t>
   </si>
   <si>
@@ -317,6 +326,9 @@
   </si>
   <si>
     <t>Week 4</t>
+  </si>
+  <si>
+    <t>Week 5</t>
   </si>
   <si>
     <t>Week</t>
@@ -738,28 +750,28 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
         <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K2" t="s">
         <v>10</v>
@@ -776,10 +788,10 @@
         <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
         <v>11</v>
@@ -797,7 +809,7 @@
         <v>11</v>
       </c>
       <c r="K3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -805,7 +817,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
@@ -826,7 +838,7 @@
         <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J4" t="s">
         <v>13</v>
@@ -840,13 +852,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
         <v>13</v>
@@ -861,7 +873,7 @@
         <v>13</v>
       </c>
       <c r="I5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J5" t="s">
         <v>13</v>
@@ -878,22 +890,22 @@
         <v>11</v>
       </c>
       <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
         <v>13</v>
       </c>
-      <c r="D6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" t="s">
-        <v>14</v>
-      </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
         <v>11</v>
       </c>
       <c r="H6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I6" t="s">
         <v>11</v>
@@ -910,13 +922,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -925,19 +937,19 @@
         <v>10</v>
       </c>
       <c r="G7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -945,34 +957,34 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F8" t="s">
         <v>10</v>
       </c>
       <c r="G8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I8" t="s">
         <v>10</v>
       </c>
       <c r="J8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -980,34 +992,34 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" t="s">
         <v>12</v>
       </c>
-      <c r="C9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I9" t="s">
+        <v>10</v>
+      </c>
+      <c r="J9" t="s">
         <v>12</v>
       </c>
-      <c r="I9" t="s">
-        <v>10</v>
-      </c>
-      <c r="J9" t="s">
-        <v>11</v>
-      </c>
       <c r="K9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1018,19 +1030,19 @@
         <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" t="s">
         <v>13</v>
       </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H10" t="s">
         <v>11</v>
@@ -1042,7 +1054,7 @@
         <v>13</v>
       </c>
       <c r="K10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1053,16 +1065,16 @@
         <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" t="s">
         <v>13</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G11" t="s">
         <v>11</v>
@@ -1074,7 +1086,7 @@
         <v>11</v>
       </c>
       <c r="J11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K11" t="s">
         <v>11</v>
@@ -1087,30 +1099,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1118,22 +1130,22 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>-11</v>
+        <v>18</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="G2">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H2" t="s">
         <v>0</v>
@@ -1144,25 +1156,25 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E3">
-        <v>-2</v>
+        <v>-11</v>
       </c>
       <c r="F3">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H3" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1170,22 +1182,22 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="F4">
-        <v>-4</v>
+        <v>6</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H4" t="s">
         <v>9</v>
@@ -1196,25 +1208,25 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>-8</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1225,21 +1237,99 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>-4</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s">
         <v>3</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E7">
+        <v>-4</v>
+      </c>
+      <c r="F7">
+        <v>-1</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="E6">
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8">
+        <v>5</v>
+      </c>
+      <c r="F8">
+        <v>4</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9">
         <v>8</v>
       </c>
-      <c r="F6">
+      <c r="F9">
         <v>7</v>
       </c>
-      <c r="G6">
+      <c r="G9">
         <v>1</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H9" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1255,13 +1345,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1272,7 +1362,7 @@
         <v>3</v>
       </c>
       <c r="C2">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="D2" t="s">
         <v>13</v>
@@ -1283,13 +1373,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1297,13 +1387,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1311,13 +1401,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C5">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1325,13 +1415,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1339,13 +1429,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1353,10 +1443,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
@@ -1367,13 +1457,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C9">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1381,10 +1471,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="D10" t="s">
         <v>10</v>
@@ -1395,10 +1485,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C11">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="D11" t="s">
         <v>10</v>
@@ -1416,16 +1506,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1436,13 +1526,13 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="D2">
-        <v>-0.2999999999999998</v>
+        <v>0.09999999999999964</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1450,16 +1540,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="D3">
-        <v>-0.1000000000000001</v>
+        <v>0.2000000000000002</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1467,16 +1557,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="D4">
-        <v>-0.3999999999999999</v>
+        <v>0.2000000000000002</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1484,16 +1574,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C5">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="D5">
-        <v>0.2999999999999998</v>
+        <v>-1.1</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1501,16 +1591,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C6">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="D6">
-        <v>-1.2</v>
+        <v>-0.5</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1518,16 +1608,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="D7">
-        <v>-0.2</v>
+        <v>-1.6</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1535,16 +1625,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="D8">
-        <v>0.5</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1552,13 +1642,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C9">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="D9">
-        <v>0.3999999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="E9" t="s">
         <v>13</v>
@@ -1569,13 +1659,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C10">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="D10">
-        <v>0.3999999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="E10" t="s">
         <v>13</v>
@@ -1589,10 +1679,10 @@
         <v>2</v>
       </c>
       <c r="C11">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="D11">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E11" t="s">
         <v>14</v>
@@ -1610,40 +1700,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -1651,22 +1741,22 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>81</v>
+        <v>63.4</v>
       </c>
       <c r="C2">
-        <v>13.2</v>
+        <v>20.7</v>
       </c>
       <c r="D2">
-        <v>4.1</v>
+        <v>10.2</v>
       </c>
       <c r="E2">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="F2">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1686,40 +1776,40 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B3">
-        <v>7.2</v>
+        <v>15</v>
       </c>
       <c r="C3">
-        <v>29.3</v>
+        <v>25.9</v>
       </c>
       <c r="D3">
-        <v>30.3</v>
+        <v>22.8</v>
       </c>
       <c r="E3">
-        <v>22.6</v>
+        <v>15.7</v>
       </c>
       <c r="F3">
-        <v>8.1</v>
+        <v>11.3</v>
       </c>
       <c r="G3">
-        <v>2.2</v>
+        <v>7.3</v>
       </c>
       <c r="H3">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>99.7</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1727,28 +1817,28 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>8.9</v>
+        <v>11.6</v>
       </c>
       <c r="C4">
-        <v>37.5</v>
+        <v>24.3</v>
       </c>
       <c r="D4">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E4">
-        <v>15.9</v>
+        <v>17</v>
       </c>
       <c r="F4">
-        <v>7</v>
+        <v>12.9</v>
       </c>
       <c r="G4">
-        <v>1.1</v>
+        <v>7.7</v>
       </c>
       <c r="H4">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1757,45 +1847,45 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>99.40000000000001</v>
+        <v>96.5</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B5">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="C5">
-        <v>16.5</v>
+        <v>12.8</v>
       </c>
       <c r="D5">
-        <v>26.1</v>
+        <v>16.7</v>
       </c>
       <c r="E5">
-        <v>31.7</v>
+        <v>25.2</v>
       </c>
       <c r="F5">
-        <v>13.5</v>
+        <v>19.5</v>
       </c>
       <c r="G5">
-        <v>6.5</v>
+        <v>14.2</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>6.4</v>
       </c>
       <c r="I5">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J5">
         <v>0.1</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L5">
-        <v>97</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1803,37 +1893,37 @@
         <v>0</v>
       </c>
       <c r="B6">
-        <v>0.2</v>
+        <v>4.7</v>
       </c>
       <c r="C6">
-        <v>3.1</v>
+        <v>10.6</v>
       </c>
       <c r="D6">
-        <v>7.2</v>
+        <v>16.7</v>
       </c>
       <c r="E6">
-        <v>17.2</v>
+        <v>20</v>
       </c>
       <c r="F6">
-        <v>39.3</v>
+        <v>23</v>
       </c>
       <c r="G6">
-        <v>21.1</v>
+        <v>16.2</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>6.9</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J6">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>88.09999999999999</v>
+        <v>91.2</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1841,80 +1931,80 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="C7">
-        <v>0.3</v>
+        <v>4.8</v>
       </c>
       <c r="D7">
-        <v>2.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E7">
-        <v>7.2</v>
+        <v>13.5</v>
       </c>
       <c r="F7">
-        <v>17.3</v>
+        <v>19.2</v>
       </c>
       <c r="G7">
-        <v>32.5</v>
+        <v>27.6</v>
       </c>
       <c r="H7">
-        <v>24.2</v>
+        <v>18.8</v>
       </c>
       <c r="I7">
-        <v>11</v>
+        <v>5.6</v>
       </c>
       <c r="J7">
-        <v>4.7</v>
+        <v>0.9</v>
       </c>
       <c r="K7">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>59.7</v>
+        <v>74.7</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
       <c r="C8">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="D8">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="E8">
-        <v>1.9</v>
+        <v>4.3</v>
       </c>
       <c r="F8">
-        <v>6.5</v>
+        <v>8.6</v>
       </c>
       <c r="G8">
-        <v>16.3</v>
+        <v>18</v>
       </c>
       <c r="H8">
-        <v>26.8</v>
+        <v>37.1</v>
       </c>
       <c r="I8">
-        <v>25.6</v>
+        <v>24.6</v>
       </c>
       <c r="J8">
-        <v>20.2</v>
+        <v>4.1</v>
       </c>
       <c r="K8">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="L8">
-        <v>25.4</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1923,36 +2013,36 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E9">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="F9">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="G9">
-        <v>10.3</v>
+        <v>7.5</v>
       </c>
       <c r="H9">
-        <v>19.6</v>
+        <v>22.4</v>
       </c>
       <c r="I9">
-        <v>30.6</v>
+        <v>50.1</v>
       </c>
       <c r="J9">
-        <v>31.3</v>
+        <v>14.7</v>
       </c>
       <c r="K9">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="L9">
-        <v>15.4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1964,28 +2054,28 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>3.7</v>
+        <v>0.3</v>
       </c>
       <c r="G10">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>18.1</v>
+        <v>3.8</v>
       </c>
       <c r="I10">
-        <v>26.7</v>
+        <v>15.6</v>
       </c>
       <c r="J10">
-        <v>35.1</v>
+        <v>73</v>
       </c>
       <c r="K10">
-        <v>4.8</v>
+        <v>6.3</v>
       </c>
       <c r="L10">
-        <v>15.3</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2011,16 +2101,16 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>2.2</v>
+        <v>0.3</v>
       </c>
       <c r="J11">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="K11">
-        <v>89.7</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -2033,35 +2123,38 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>37</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B2">
-        <v>99.2</v>
+        <v>98.7</v>
       </c>
       <c r="C2">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="D2">
         <v>100</v>
@@ -2070,186 +2163,216 @@
         <v>100</v>
       </c>
       <c r="F2">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="G2">
+        <v>99.7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3">
-        <v>62.1</v>
-      </c>
       <c r="C3">
-        <v>94.39999999999999</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="D3">
-        <v>97.5</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="E3">
-        <v>99.40000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="F3">
-        <v>99.59999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>96.2</v>
+      </c>
+      <c r="G3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B4">
-        <v>97.5</v>
+        <v>97.7</v>
       </c>
       <c r="C4">
         <v>100</v>
       </c>
       <c r="D4">
-        <v>99.09999999999999</v>
+        <v>99.2</v>
       </c>
       <c r="E4">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="F4">
+        <v>98</v>
+      </c>
+      <c r="G4">
+        <v>96.59999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>64.5</v>
+      </c>
+      <c r="C5">
+        <v>95.39999999999999</v>
+      </c>
+      <c r="D5">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="E5">
         <v>99.7</v>
       </c>
-      <c r="F4">
-        <v>99.59999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5">
-        <v>100</v>
-      </c>
-      <c r="C5">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="D5">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="E5">
-        <v>98</v>
-      </c>
       <c r="F5">
-        <v>98.40000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>92.5</v>
+      </c>
+      <c r="G5">
+        <v>92.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B6">
-        <v>57.99999999999999</v>
+        <v>58.2</v>
       </c>
       <c r="C6">
-        <v>27.8</v>
+        <v>31.7</v>
       </c>
       <c r="D6">
-        <v>40</v>
+        <v>38.9</v>
       </c>
       <c r="E6">
-        <v>89.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="F6">
-        <v>88.09999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>86.3</v>
+      </c>
+      <c r="G6">
+        <v>91.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B7">
-        <v>7.000000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="C7">
-        <v>46.9</v>
+        <v>43.8</v>
       </c>
       <c r="D7">
-        <v>24.4</v>
+        <v>26.2</v>
       </c>
       <c r="E7">
-        <v>59.59999999999999</v>
+        <v>61</v>
       </c>
       <c r="F7">
-        <v>59.7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="G7">
+        <v>72.09999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>38.8</v>
+      </c>
+      <c r="C8">
+        <v>48.3</v>
+      </c>
+      <c r="D8">
+        <v>73.3</v>
+      </c>
+      <c r="E8">
+        <v>16.5</v>
+      </c>
+      <c r="F8">
+        <v>42.5</v>
+      </c>
+      <c r="G8">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>99.8</v>
+      </c>
+      <c r="C9">
+        <v>75.8</v>
+      </c>
+      <c r="D9">
+        <v>19.9</v>
+      </c>
+      <c r="E9">
+        <v>11.2</v>
+      </c>
+      <c r="F9">
+        <v>10.8</v>
+      </c>
+      <c r="G9">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B8">
-        <v>0.5</v>
-      </c>
-      <c r="C8">
-        <v>3.8</v>
-      </c>
-      <c r="D8">
-        <v>47.3</v>
-      </c>
-      <c r="E8">
-        <v>26.3</v>
-      </c>
-      <c r="F8">
-        <v>24.7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9">
-        <v>36.6</v>
-      </c>
-      <c r="C9">
-        <v>48.5</v>
-      </c>
-      <c r="D9">
-        <v>70.59999999999999</v>
-      </c>
-      <c r="E9">
-        <v>16.2</v>
-      </c>
-      <c r="F9">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="B10">
-        <v>99.90000000000001</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="C10">
-        <v>77.90000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="D10">
-        <v>21</v>
+        <v>44.4</v>
       </c>
       <c r="E10">
-        <v>11.6</v>
+        <v>22.9</v>
       </c>
       <c r="F10">
-        <v>13.9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>1.2</v>
+      </c>
+      <c r="G10">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B11">
-        <v>39.2</v>
+        <v>34.1</v>
       </c>
       <c r="C11">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="D11">
+        <v>0.1</v>
+      </c>
+      <c r="E11">
         <v>0.2</v>
       </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
       <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
         <v>0</v>
       </c>
     </row>
@@ -2265,28 +2388,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2294,28 +2417,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D2">
-        <v>126.56</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>130.98</v>
+        <v>133.24</v>
       </c>
       <c r="G2">
-        <v>0.525</v>
+        <v>0.556</v>
       </c>
       <c r="H2">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2323,28 +2446,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D3">
-        <v>95.62</v>
+        <v>130.77</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>130.08</v>
+        <v>129.16</v>
       </c>
       <c r="G3">
-        <v>0.525</v>
+        <v>0.467</v>
       </c>
       <c r="H3">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="I3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2352,28 +2475,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4">
+        <v>138.47</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4">
+        <v>128.31</v>
+      </c>
+      <c r="G4">
+        <v>0.467</v>
+      </c>
+      <c r="H4">
+        <v>0.4</v>
+      </c>
+      <c r="I4">
         <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D4">
-        <v>123.64</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4">
-        <v>130.06</v>
-      </c>
-      <c r="G4">
-        <v>0.525</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2384,25 +2507,25 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D5">
-        <v>116.34</v>
+        <v>125.5</v>
       </c>
       <c r="E5" t="s">
         <v>13</v>
       </c>
       <c r="F5">
-        <v>130.99</v>
+        <v>129.75</v>
       </c>
       <c r="G5">
-        <v>0.525</v>
+        <v>0.533</v>
       </c>
       <c r="H5">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="I5">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2410,28 +2533,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D6">
-        <v>144.31</v>
+        <v>130.69</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F6">
-        <v>125.84</v>
+        <v>129.17</v>
       </c>
       <c r="G6">
-        <v>0.45</v>
+        <v>0.489</v>
       </c>
       <c r="H6">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2442,25 +2565,25 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D7">
-        <v>120.63</v>
+        <v>107.75</v>
       </c>
       <c r="E7" t="s">
         <v>13</v>
       </c>
       <c r="F7">
-        <v>130.58</v>
+        <v>131.72</v>
       </c>
       <c r="G7">
-        <v>0.55</v>
+        <v>0.533</v>
       </c>
       <c r="H7">
-        <v>-0.5</v>
+        <v>0.1</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2468,28 +2591,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D8">
-        <v>144.16</v>
+        <v>127.5</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F8">
-        <v>125.43</v>
+        <v>129.53</v>
       </c>
       <c r="G8">
-        <v>0.475</v>
+        <v>0.511</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>-0.2</v>
       </c>
       <c r="I8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2500,25 +2623,25 @@
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D9">
-        <v>142.16</v>
+        <v>139.08</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F9">
-        <v>126.36</v>
+        <v>128.24</v>
       </c>
       <c r="G9">
-        <v>0.475</v>
+        <v>0.489</v>
       </c>
       <c r="H9">
-        <v>-1.2</v>
+        <v>-0.7</v>
       </c>
       <c r="I9">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2526,28 +2649,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D10">
-        <v>114.38</v>
+        <v>147.82</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F10">
-        <v>126.33</v>
+        <v>127.27</v>
       </c>
       <c r="G10">
-        <v>0.475</v>
+        <v>0.489</v>
       </c>
       <c r="H10">
-        <v>-1.8</v>
+        <v>-1.1</v>
       </c>
       <c r="I10">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2558,25 +2681,25 @@
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D11">
-        <v>154.29</v>
+        <v>151.57</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F11">
-        <v>125.44</v>
+        <v>126.85</v>
       </c>
       <c r="G11">
-        <v>0.475</v>
+        <v>0.467</v>
       </c>
       <c r="H11">
-        <v>-3.1</v>
+        <v>-2</v>
       </c>
       <c r="I11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -2591,31 +2714,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2623,16 +2746,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D2">
-        <v>154.29</v>
+        <v>151.568</v>
       </c>
       <c r="E2">
-        <v>617.16</v>
+        <v>757.8399999999999</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -2641,39 +2764,39 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C3">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="D3">
-        <v>142.165</v>
+        <v>147.816</v>
       </c>
       <c r="E3">
-        <v>568.66</v>
+        <v>739.0800000000002</v>
       </c>
       <c r="F3">
-        <v>99.7</v>
+        <v>98</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2681,57 +2804,57 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C4">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="D4">
-        <v>144.315</v>
+        <v>138.468</v>
       </c>
       <c r="E4">
-        <v>577.26</v>
+        <v>692.34</v>
       </c>
       <c r="F4">
-        <v>99.40000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C5">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D5">
-        <v>144.16</v>
+        <v>139.08</v>
       </c>
       <c r="E5">
-        <v>576.6400000000001</v>
+        <v>695.4</v>
       </c>
       <c r="F5">
-        <v>97</v>
+        <v>92.30000000000001</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2739,25 +2862,25 @@
         <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C6">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="D6">
-        <v>126.56</v>
+        <v>130.768</v>
       </c>
       <c r="E6">
-        <v>506.24</v>
+        <v>653.84</v>
       </c>
       <c r="F6">
-        <v>88.09999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I6" t="s">
         <v>80</v>
@@ -2768,25 +2891,25 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D7">
-        <v>123.635</v>
+        <v>130.692</v>
       </c>
       <c r="E7">
-        <v>494.5400000000001</v>
+        <v>653.46</v>
       </c>
       <c r="F7">
-        <v>59.7</v>
+        <v>74.7</v>
       </c>
       <c r="G7">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I7" t="s">
         <v>81</v>
@@ -2794,28 +2917,28 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C8">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="D8">
-        <v>120.63</v>
+        <v>127.504</v>
       </c>
       <c r="E8">
-        <v>482.52</v>
+        <v>637.52</v>
       </c>
       <c r="F8">
-        <v>25.4</v>
+        <v>34</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="H8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I8" t="s">
         <v>82</v>
@@ -2823,60 +2946,60 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C9">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="D9">
-        <v>114.375</v>
+        <v>125.496</v>
       </c>
       <c r="E9">
-        <v>457.5</v>
+        <v>627.48</v>
       </c>
       <c r="F9">
-        <v>15.4</v>
+        <v>12</v>
       </c>
       <c r="G9">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="H9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C10">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="D10">
-        <v>116.345</v>
+        <v>107.752</v>
       </c>
       <c r="E10">
-        <v>465.38</v>
+        <v>538.76</v>
       </c>
       <c r="F10">
-        <v>15.3</v>
+        <v>1.3</v>
       </c>
       <c r="G10">
-        <v>4.8</v>
+        <v>6.3</v>
       </c>
       <c r="H10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2884,28 +3007,28 @@
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>95.62</v>
+        <v>94.10400000000001</v>
       </c>
       <c r="E11">
-        <v>382.48</v>
+        <v>470.52</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>89.7</v>
+        <v>92.60000000000001</v>
       </c>
       <c r="H11" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -2920,19 +3043,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2943,16 +3066,16 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2960,19 +3083,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2983,13 +3106,13 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
         <v>89</v>
@@ -3000,19 +3123,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3020,19 +3143,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3040,16 +3163,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
         <v>91</v>
@@ -3060,19 +3183,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D8">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3080,19 +3203,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D9">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3103,16 +3226,16 @@
         <v>0</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D10">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3123,7 +3246,7 @@
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D11">
         <v>-17</v>
@@ -3132,7 +3255,7 @@
         <v>14</v>
       </c>
       <c r="F11" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -3142,27 +3265,30 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>101</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -3178,31 +3304,37 @@
       <c r="E2">
         <v>19</v>
       </c>
-      <c r="F2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="F2">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B3">
-        <v>-2</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>10</v>
+      </c>
+      <c r="G3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -3218,111 +3350,129 @@
       <c r="E4">
         <v>7</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4">
+        <v>6</v>
+      </c>
+      <c r="G4" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>-2</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>8</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>-1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>-8</v>
+      </c>
+      <c r="C7">
+        <v>-8</v>
+      </c>
+      <c r="D7">
+        <v>-5</v>
+      </c>
+      <c r="E7">
+        <v>-4</v>
+      </c>
+      <c r="F7">
+        <v>-2</v>
+      </c>
+      <c r="G7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>-2</v>
+      </c>
+      <c r="D8">
+        <v>-11</v>
+      </c>
+      <c r="E8">
+        <v>-8</v>
+      </c>
+      <c r="F8">
+        <v>-2</v>
+      </c>
+      <c r="G8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B5">
+      <c r="B9">
         <v>4</v>
       </c>
-      <c r="C5">
+      <c r="C9">
         <v>8</v>
       </c>
-      <c r="D5">
+      <c r="D9">
         <v>5</v>
       </c>
-      <c r="E5">
+      <c r="E9">
         <v>4</v>
       </c>
-      <c r="F5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
+      <c r="F9">
         <v>-4</v>
       </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>5</v>
-      </c>
-      <c r="D7">
-        <v>4</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>-8</v>
-      </c>
-      <c r="C8">
-        <v>-8</v>
-      </c>
-      <c r="D8">
-        <v>-5</v>
-      </c>
-      <c r="E8">
-        <v>-4</v>
-      </c>
-      <c r="F8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>-2</v>
-      </c>
-      <c r="D9">
-        <v>-11</v>
-      </c>
-      <c r="E9">
-        <v>-8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="G9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -3338,11 +3488,14 @@
       <c r="E10">
         <v>-11</v>
       </c>
-      <c r="F10" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="F10">
+        <v>-10</v>
+      </c>
+      <c r="G10" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
         <v>2</v>
       </c>
@@ -3358,8 +3511,11 @@
       <c r="E11">
         <v>-17</v>
       </c>
-      <c r="F11" t="s">
-        <v>91</v>
+      <c r="F11">
+        <v>-17</v>
+      </c>
+      <c r="G11" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/The Goofy Goobers 2026.xlsx
+++ b/data/leagues/The Goofy Goobers 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="108">
   <si>
     <t>Rice Rice Baby</t>
   </si>
@@ -55,22 +55,22 @@
     <t>Delco Football Team</t>
   </si>
   <si>
-    <t>4-1-0</t>
-  </si>
-  <si>
-    <t>3-2-0</t>
-  </si>
-  <si>
-    <t>2-3-0</t>
-  </si>
-  <si>
-    <t>1-4-0</t>
-  </si>
-  <si>
-    <t>0-5-0</t>
-  </si>
-  <si>
-    <t>5-0-0</t>
+    <t>4-2-0</t>
+  </si>
+  <si>
+    <t>5-1-0</t>
+  </si>
+  <si>
+    <t>3-3-0</t>
+  </si>
+  <si>
+    <t>2-4-0</t>
+  </si>
+  <si>
+    <t>1-5-0</t>
+  </si>
+  <si>
+    <t>0-6-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -142,6 +142,9 @@
     <t>Week_6</t>
   </si>
   <si>
+    <t>Week_7</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -163,30 +166,30 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>Marvin Ta</t>
+  </si>
+  <si>
     <t>Samuel DiPasqua</t>
   </si>
   <si>
-    <t>Marvin Ta</t>
+    <t>Anthony Rizzo</t>
+  </si>
+  <si>
+    <t>Stan Yu</t>
+  </si>
+  <si>
+    <t>Derrick Edmiston</t>
+  </si>
+  <si>
+    <t>Prahlad Singh</t>
   </si>
   <si>
     <t>Horatio Kneepads</t>
   </si>
   <si>
-    <t>Stan Yu</t>
-  </si>
-  <si>
     <t>Bridget Cashel</t>
   </si>
   <si>
-    <t>Derrick Edmiston</t>
-  </si>
-  <si>
-    <t>Prahlad Singh</t>
-  </si>
-  <si>
-    <t>Anthony Rizzo</t>
-  </si>
-  <si>
     <t>Andrew Bock</t>
   </si>
   <si>
@@ -217,72 +220,63 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>4-1</t>
-  </si>
-  <si>
-    <t>3-2</t>
-  </si>
-  <si>
-    <t>2-3</t>
-  </si>
-  <si>
-    <t>1-4</t>
-  </si>
-  <si>
-    <t>0-5</t>
-  </si>
-  <si>
-    <t>10.7-3.2-0.1</t>
+    <t>4-2</t>
+  </si>
+  <si>
+    <t>3-3</t>
+  </si>
+  <si>
+    <t>1-5</t>
+  </si>
+  <si>
+    <t>9.6-4.4-0.1</t>
+  </si>
+  <si>
+    <t>9.6-4.3-0.1</t>
+  </si>
+  <si>
+    <t>9.0-4.9-0.1</t>
   </si>
   <si>
     <t>9.1-4.8-0.1</t>
   </si>
   <si>
-    <t>9.3-4.7-0.1</t>
-  </si>
-  <si>
-    <t>8.4-5.5-0.1</t>
-  </si>
-  <si>
-    <t>8.6-5.3-0.1</t>
-  </si>
-  <si>
-    <t>7.6-6.4-0.1</t>
-  </si>
-  <si>
-    <t>6.2-7.7-0.1</t>
-  </si>
-  <si>
-    <t>5.0-8.9-0.1</t>
-  </si>
-  <si>
-    <t>3.6-10.3-0.1</t>
-  </si>
-  <si>
-    <t>1.2-12.8-0.1</t>
-  </si>
-  <si>
-    <t>11-3</t>
+    <t>8.8-5.1-0.1</t>
+  </si>
+  <si>
+    <t>7.2-6.7-0.1</t>
+  </si>
+  <si>
+    <t>6.6-7.3-0.1</t>
+  </si>
+  <si>
+    <t>4.4-9.5-0.1</t>
+  </si>
+  <si>
+    <t>2.2-11.7-0.1</t>
+  </si>
+  <si>
+    <t>3.1-10.8-0.1</t>
+  </si>
+  <si>
+    <t>10-4</t>
   </si>
   <si>
     <t>9-5</t>
   </si>
   <si>
-    <t>8-6</t>
-  </si>
-  <si>
-    <t>6-8</t>
-  </si>
-  <si>
-    <t>5-9</t>
+    <t>7-7</t>
+  </si>
+  <si>
+    <t>4-10</t>
+  </si>
+  <si>
+    <t>2-12</t>
   </si>
   <si>
     <t>3-11</t>
   </si>
   <si>
-    <t>1-13</t>
-  </si>
-  <si>
     <t>Owners</t>
   </si>
   <si>
@@ -292,30 +286,30 @@
     <t>Change From Last Week</t>
   </si>
   <si>
-    <t>↓1</t>
+    <t>↑1</t>
+  </si>
+  <si>
+    <t>↑11</t>
+  </si>
+  <si>
+    <t>↑4</t>
+  </si>
+  <si>
+    <t>↓2</t>
   </si>
   <si>
     <t>↑9</t>
   </si>
   <si>
-    <t>↑2</t>
-  </si>
-  <si>
-    <t>↓9</t>
-  </si>
-  <si>
-    <t>↑6</t>
+    <t>↓4</t>
+  </si>
+  <si>
+    <t>↓5</t>
   </si>
   <si>
     <t>↓8</t>
   </si>
   <si>
-    <t>↑1</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>Week 1</t>
   </si>
   <si>
@@ -329,6 +323,9 @@
   </si>
   <si>
     <t>Week 5</t>
+  </si>
+  <si>
+    <t>Week 6</t>
   </si>
   <si>
     <t>Week</t>
@@ -753,25 +750,25 @@
         <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H2" t="s">
         <v>12</v>
       </c>
       <c r="I2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K2" t="s">
         <v>10</v>
@@ -782,23 +779,23 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
       </c>
       <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" t="s">
         <v>11</v>
       </c>
-      <c r="G3" t="s">
-        <v>10</v>
-      </c>
       <c r="H3" t="s">
         <v>10</v>
       </c>
@@ -806,7 +803,7 @@
         <v>10</v>
       </c>
       <c r="J3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K3" t="s">
         <v>12</v>
@@ -817,22 +814,22 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F4" t="s">
         <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H4" t="s">
         <v>14</v>
@@ -841,10 +838,10 @@
         <v>13</v>
       </c>
       <c r="J4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -852,34 +849,34 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H5" t="s">
         <v>13</v>
       </c>
       <c r="I5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -887,7 +884,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
@@ -902,19 +899,19 @@
         <v>12</v>
       </c>
       <c r="G6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H6" t="s">
         <v>12</v>
       </c>
       <c r="I6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -922,34 +919,34 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
         <v>11</v>
       </c>
-      <c r="C7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" t="s">
-        <v>10</v>
-      </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G7" t="s">
         <v>10</v>
       </c>
       <c r="H7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I7" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J7" t="s">
         <v>10</v>
       </c>
       <c r="K7" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -957,34 +954,34 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
         <v>11</v>
       </c>
-      <c r="C8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="G8" t="s">
         <v>12</v>
       </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" t="s">
-        <v>10</v>
-      </c>
       <c r="H8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I8" t="s">
         <v>10</v>
       </c>
       <c r="J8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -992,10 +989,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D9" t="s">
         <v>12</v>
@@ -1007,19 +1004,19 @@
         <v>12</v>
       </c>
       <c r="G9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" t="s">
         <v>11</v>
       </c>
-      <c r="H9" t="s">
-        <v>10</v>
-      </c>
       <c r="I9" t="s">
         <v>10</v>
       </c>
       <c r="J9" t="s">
+        <v>10</v>
+      </c>
+      <c r="K9" t="s">
         <v>12</v>
-      </c>
-      <c r="K9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1027,34 +1024,34 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" t="s">
         <v>12</v>
       </c>
-      <c r="D10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="J10" t="s">
+        <v>14</v>
+      </c>
+      <c r="K10" t="s">
         <v>13</v>
-      </c>
-      <c r="G10" t="s">
-        <v>12</v>
-      </c>
-      <c r="H10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I10" t="s">
-        <v>11</v>
-      </c>
-      <c r="J10" t="s">
-        <v>13</v>
-      </c>
-      <c r="K10" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1062,10 +1059,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D11" t="s">
         <v>13</v>
@@ -1077,19 +1074,19 @@
         <v>12</v>
       </c>
       <c r="G11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" t="s">
         <v>11</v>
       </c>
-      <c r="H11" t="s">
-        <v>10</v>
-      </c>
       <c r="I11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J11" t="s">
         <v>11</v>
       </c>
       <c r="K11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1099,30 +1096,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1139,13 +1136,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="G2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H2" t="s">
         <v>0</v>
@@ -1165,10 +1162,10 @@
         <v>4</v>
       </c>
       <c r="E3">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3">
         <v>11</v>
@@ -1182,25 +1179,25 @@
         <v>2</v>
       </c>
       <c r="B4">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
         <v>5</v>
       </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>6</v>
-      </c>
       <c r="E4">
-        <v>-2</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="G4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H4" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1208,22 +1205,22 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>8</v>
       </c>
-      <c r="D5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5">
-        <v>-2</v>
-      </c>
-      <c r="F5">
-        <v>-8</v>
-      </c>
       <c r="G5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H5" t="s">
         <v>9</v>
@@ -1243,13 +1240,13 @@
         <v>9</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <v>-4</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H6" t="s">
         <v>9</v>
@@ -1260,25 +1257,25 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E7">
         <v>-4</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>-8</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1286,25 +1283,25 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C8" t="s">
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H8" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1312,25 +1309,51 @@
         <v>7</v>
       </c>
       <c r="B9">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <v>-16</v>
+      </c>
+      <c r="F9">
+        <v>-19</v>
+      </c>
+      <c r="G9">
+        <v>3</v>
+      </c>
+      <c r="H9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" t="s">
         <v>4</v>
       </c>
-      <c r="C9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9">
-        <v>8</v>
-      </c>
-      <c r="F9">
-        <v>7</v>
-      </c>
-      <c r="G9">
+      <c r="E10">
+        <v>5</v>
+      </c>
+      <c r="F10">
+        <v>4</v>
+      </c>
+      <c r="G10">
         <v>1</v>
       </c>
-      <c r="H9" t="s">
-        <v>6</v>
+      <c r="H10" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1362,10 +1385,10 @@
         <v>3</v>
       </c>
       <c r="C2">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1376,7 +1399,7 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
@@ -1390,7 +1413,7 @@
         <v>4</v>
       </c>
       <c r="C4">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
@@ -1401,13 +1424,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1415,13 +1438,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C6">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1429,13 +1452,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C7">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1443,13 +1466,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1457,13 +1480,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C9">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1471,10 +1494,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="D10" t="s">
         <v>10</v>
@@ -1485,10 +1508,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="D11" t="s">
         <v>10</v>
@@ -1526,10 +1549,10 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="D2">
-        <v>0.09999999999999964</v>
+        <v>0.5</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -1543,13 +1566,13 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="D3">
-        <v>0.2000000000000002</v>
+        <v>-0.1000000000000001</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1560,13 +1583,13 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="D4">
-        <v>0.2000000000000002</v>
+        <v>-0.1000000000000001</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1577,10 +1600,10 @@
         <v>7</v>
       </c>
       <c r="C5">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="D5">
-        <v>-1.1</v>
+        <v>-0.2000000000000002</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -1594,13 +1617,13 @@
         <v>9</v>
       </c>
       <c r="C6">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="D6">
-        <v>-0.5</v>
+        <v>-0.2999999999999998</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1608,16 +1631,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1625,16 +1648,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="D8">
-        <v>0.3999999999999999</v>
+        <v>-1.5</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1645,13 +1668,13 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="D9">
-        <v>1.1</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1662,13 +1685,13 @@
         <v>3</v>
       </c>
       <c r="C10">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="D10">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1679,10 +1702,10 @@
         <v>2</v>
       </c>
       <c r="C11">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="D11">
-        <v>0.7</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="E11" t="s">
         <v>14</v>
@@ -1738,31 +1761,31 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B2">
-        <v>63.4</v>
+        <v>32.1</v>
       </c>
       <c r="C2">
-        <v>20.7</v>
+        <v>24.1</v>
       </c>
       <c r="D2">
-        <v>10.2</v>
+        <v>17.5</v>
       </c>
       <c r="E2">
-        <v>3.5</v>
+        <v>12.4</v>
       </c>
       <c r="F2">
-        <v>1.7</v>
+        <v>8.5</v>
       </c>
       <c r="G2">
-        <v>0.5</v>
+        <v>4.3</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1771,74 +1794,74 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B3">
-        <v>15</v>
+        <v>30.9</v>
       </c>
       <c r="C3">
-        <v>25.9</v>
+        <v>24.2</v>
       </c>
       <c r="D3">
-        <v>22.8</v>
+        <v>18.4</v>
       </c>
       <c r="E3">
-        <v>15.7</v>
+        <v>12.5</v>
       </c>
       <c r="F3">
-        <v>11.3</v>
+        <v>7.6</v>
       </c>
       <c r="G3">
-        <v>7.3</v>
+        <v>4.7</v>
       </c>
       <c r="H3">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="I3">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>98</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B4">
-        <v>11.6</v>
+        <v>11</v>
       </c>
       <c r="C4">
-        <v>24.3</v>
+        <v>16.2</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>21.4</v>
       </c>
       <c r="E4">
-        <v>17</v>
+        <v>20.5</v>
       </c>
       <c r="F4">
-        <v>12.9</v>
+        <v>19.5</v>
       </c>
       <c r="G4">
-        <v>7.7</v>
+        <v>8.9</v>
       </c>
       <c r="H4">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="I4">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1847,74 +1870,74 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>96.5</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5">
-        <v>3.9</v>
+        <v>14.1</v>
       </c>
       <c r="C5">
-        <v>12.8</v>
+        <v>17.8</v>
       </c>
       <c r="D5">
-        <v>16.7</v>
+        <v>20.9</v>
       </c>
       <c r="E5">
-        <v>25.2</v>
+        <v>21.1</v>
       </c>
       <c r="F5">
-        <v>19.5</v>
+        <v>16.8</v>
       </c>
       <c r="G5">
-        <v>14.2</v>
+        <v>6.2</v>
       </c>
       <c r="H5">
-        <v>6.4</v>
+        <v>2.9</v>
       </c>
       <c r="I5">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="J5">
         <v>0.1</v>
       </c>
       <c r="K5">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>92.3</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>4.7</v>
+        <v>10.9</v>
       </c>
       <c r="C6">
-        <v>10.6</v>
+        <v>14</v>
       </c>
       <c r="D6">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E6">
-        <v>20</v>
+        <v>21.9</v>
       </c>
       <c r="F6">
-        <v>23</v>
+        <v>20.8</v>
       </c>
       <c r="G6">
-        <v>16.2</v>
+        <v>12.9</v>
       </c>
       <c r="H6">
-        <v>6.9</v>
+        <v>3.3</v>
       </c>
       <c r="I6">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1923,45 +1946,45 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>91.2</v>
+        <v>96.5</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B7">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="C7">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="D7">
-        <v>8.199999999999999</v>
+        <v>3.3</v>
       </c>
       <c r="E7">
-        <v>13.5</v>
+        <v>7.9</v>
       </c>
       <c r="F7">
-        <v>19.2</v>
+        <v>14.7</v>
       </c>
       <c r="G7">
-        <v>27.6</v>
+        <v>31.8</v>
       </c>
       <c r="H7">
-        <v>18.8</v>
+        <v>29.9</v>
       </c>
       <c r="I7">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="J7">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>74.7</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1969,37 +1992,37 @@
         <v>4</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="C8">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="D8">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="E8">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="F8">
-        <v>8.6</v>
+        <v>11.2</v>
       </c>
       <c r="G8">
-        <v>18</v>
+        <v>27.8</v>
       </c>
       <c r="H8">
-        <v>37.1</v>
+        <v>41.2</v>
       </c>
       <c r="I8">
-        <v>24.6</v>
+        <v>11.6</v>
       </c>
       <c r="J8">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="K8">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L8">
-        <v>34</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -2013,36 +2036,36 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="F9">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="G9">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="H9">
-        <v>22.4</v>
+        <v>15</v>
       </c>
       <c r="I9">
-        <v>50.1</v>
+        <v>58.8</v>
       </c>
       <c r="J9">
-        <v>14.7</v>
+        <v>17.6</v>
       </c>
       <c r="K9">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="L9">
-        <v>12</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2057,30 +2080,30 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="H10">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="I10">
-        <v>15.6</v>
+        <v>3.9</v>
       </c>
       <c r="J10">
-        <v>73</v>
+        <v>21.1</v>
       </c>
       <c r="K10">
-        <v>6.3</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="L10">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2098,22 +2121,22 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I11">
-        <v>0.3</v>
+        <v>16.3</v>
       </c>
       <c r="J11">
-        <v>7.1</v>
+        <v>59.8</v>
       </c>
       <c r="K11">
-        <v>92.59999999999999</v>
+        <v>21.4</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -2123,10 +2146,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
         <v>33</v>
       </c>
@@ -2145,16 +2168,19 @@
       <c r="G1" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B2">
-        <v>98.7</v>
+        <v>99.2</v>
       </c>
       <c r="C2">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="D2">
         <v>100</v>
@@ -2163,13 +2189,16 @@
         <v>100</v>
       </c>
       <c r="F2">
-        <v>99.90000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="G2">
-        <v>99.7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>98.5</v>
+      </c>
+      <c r="H2">
+        <v>99.2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -2180,199 +2209,226 @@
         <v>99.90000000000001</v>
       </c>
       <c r="D3">
-        <v>99.59999999999999</v>
+        <v>99.8</v>
       </c>
       <c r="E3">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
       <c r="F3">
-        <v>96.2</v>
+        <v>97.7</v>
       </c>
       <c r="G3">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="H3">
+        <v>98.40000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B4">
-        <v>97.7</v>
+        <v>98.2</v>
       </c>
       <c r="C4">
         <v>100</v>
       </c>
       <c r="D4">
-        <v>99.2</v>
+        <v>99.3</v>
       </c>
       <c r="E4">
         <v>99.90000000000001</v>
       </c>
       <c r="F4">
-        <v>98</v>
+        <v>97.8</v>
       </c>
       <c r="G4">
-        <v>96.59999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="H4">
+        <v>95.89999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B5">
-        <v>64.5</v>
+        <v>62</v>
       </c>
       <c r="C5">
-        <v>95.39999999999999</v>
+        <v>93.89999999999999</v>
       </c>
       <c r="D5">
-        <v>98.40000000000001</v>
+        <v>97.7</v>
       </c>
       <c r="E5">
         <v>99.7</v>
       </c>
       <c r="F5">
-        <v>92.5</v>
+        <v>92.30000000000001</v>
       </c>
       <c r="G5">
-        <v>92.2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>95</v>
+      </c>
+      <c r="H5">
+        <v>95.59999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B6">
-        <v>58.2</v>
+        <v>4.6</v>
       </c>
       <c r="C6">
-        <v>31.7</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="D6">
-        <v>38.9</v>
+        <v>31.8</v>
       </c>
       <c r="E6">
-        <v>90.40000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="F6">
-        <v>86.3</v>
+        <v>73.7</v>
       </c>
       <c r="G6">
-        <v>91.3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>95.5</v>
+      </c>
+      <c r="H6">
+        <v>95.59999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B7">
-        <v>7.3</v>
+        <v>61.2</v>
       </c>
       <c r="C7">
-        <v>43.8</v>
+        <v>32</v>
       </c>
       <c r="D7">
-        <v>26.2</v>
+        <v>38</v>
       </c>
       <c r="E7">
-        <v>61</v>
+        <v>88.7</v>
       </c>
       <c r="F7">
-        <v>72.59999999999999</v>
+        <v>84.89999999999999</v>
       </c>
       <c r="G7">
-        <v>72.09999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>65.10000000000001</v>
+      </c>
+      <c r="H7">
+        <v>60.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B8">
-        <v>38.8</v>
+        <v>29.8</v>
       </c>
       <c r="C8">
-        <v>48.3</v>
+        <v>40.3</v>
       </c>
       <c r="D8">
-        <v>73.3</v>
+        <v>71.7</v>
       </c>
       <c r="E8">
         <v>16.5</v>
       </c>
       <c r="F8">
-        <v>42.5</v>
+        <v>42.6</v>
       </c>
       <c r="G8">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>48.4</v>
+      </c>
+      <c r="H8">
+        <v>50.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="C9">
-        <v>75.8</v>
+        <v>83.8</v>
       </c>
       <c r="D9">
-        <v>19.9</v>
+        <v>22.4</v>
       </c>
       <c r="E9">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="F9">
         <v>11.2</v>
       </c>
-      <c r="F9">
-        <v>10.8</v>
-      </c>
       <c r="G9">
-        <v>13.9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>3.7</v>
+      </c>
+      <c r="H9">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B10">
-        <v>0.8999999999999999</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="C10">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="D10">
-        <v>44.4</v>
+        <v>39.3</v>
       </c>
       <c r="E10">
-        <v>22.9</v>
+        <v>20.4</v>
       </c>
       <c r="F10">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="G10">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>0.1</v>
+      </c>
+      <c r="H10">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B11">
-        <v>34.1</v>
+        <v>44.4</v>
       </c>
       <c r="C11">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
         <v>0.1</v>
       </c>
-      <c r="E11">
-        <v>0.2</v>
-      </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
         <v>0</v>
       </c>
     </row>
@@ -2391,25 +2447,25 @@
         <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2417,28 +2473,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D2">
-        <v>94.09999999999999</v>
+        <v>118.43</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>133.24</v>
+        <v>126.96</v>
       </c>
       <c r="G2">
-        <v>0.556</v>
+        <v>0.521</v>
       </c>
       <c r="H2">
-        <v>1.9</v>
+        <v>4.4</v>
       </c>
       <c r="I2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2446,28 +2502,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D3">
-        <v>130.77</v>
+        <v>92.67</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F3">
-        <v>129.16</v>
+        <v>126.96</v>
       </c>
       <c r="G3">
-        <v>0.467</v>
+        <v>0.521</v>
       </c>
       <c r="H3">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="I3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2475,28 +2531,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D4">
-        <v>138.47</v>
+        <v>132.12</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4">
-        <v>128.31</v>
+        <v>122.49</v>
       </c>
       <c r="G4">
-        <v>0.467</v>
+        <v>0.521</v>
       </c>
       <c r="H4">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="I4">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2507,25 +2563,25 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D5">
-        <v>125.5</v>
+        <v>114.72</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5">
-        <v>129.75</v>
+        <v>122.49</v>
       </c>
       <c r="G5">
-        <v>0.533</v>
+        <v>0.521</v>
       </c>
       <c r="H5">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2533,28 +2589,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D6">
-        <v>130.69</v>
+        <v>101.61</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F6">
-        <v>129.17</v>
+        <v>125.43</v>
       </c>
       <c r="G6">
-        <v>0.489</v>
+        <v>0.542</v>
       </c>
       <c r="H6">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="I6">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2562,28 +2618,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D7">
-        <v>107.75</v>
+        <v>121.72</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F7">
-        <v>131.72</v>
+        <v>125.43</v>
       </c>
       <c r="G7">
-        <v>0.533</v>
+        <v>0.542</v>
       </c>
       <c r="H7">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="I7">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2591,28 +2647,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D8">
-        <v>127.5</v>
+        <v>133.52</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F8">
-        <v>129.53</v>
+        <v>120.08</v>
       </c>
       <c r="G8">
-        <v>0.511</v>
+        <v>0.458</v>
       </c>
       <c r="H8">
-        <v>-0.2</v>
+        <v>-1.9</v>
       </c>
       <c r="I8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2620,28 +2676,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D9">
-        <v>139.08</v>
+        <v>132.58</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F9">
-        <v>128.24</v>
+        <v>120.08</v>
       </c>
       <c r="G9">
-        <v>0.489</v>
+        <v>0.458</v>
       </c>
       <c r="H9">
-        <v>-0.7</v>
+        <v>-1.9</v>
       </c>
       <c r="I9">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2652,25 +2708,25 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D10">
-        <v>147.82</v>
+        <v>140.3</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F10">
-        <v>127.27</v>
+        <v>118.42</v>
       </c>
       <c r="G10">
-        <v>0.489</v>
+        <v>0.458</v>
       </c>
       <c r="H10">
-        <v>-1.1</v>
+        <v>-3.8</v>
       </c>
       <c r="I10">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2681,25 +2737,25 @@
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D11">
-        <v>151.57</v>
+        <v>139.11</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11">
-        <v>126.85</v>
+        <v>118.42</v>
       </c>
       <c r="G11">
-        <v>0.467</v>
+        <v>0.458</v>
       </c>
       <c r="H11">
-        <v>-2</v>
+        <v>-3.8</v>
       </c>
       <c r="I11">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2717,202 +2773,202 @@
         <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C2">
-        <v>0.8</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D2">
-        <v>151.568</v>
+        <v>140.3033333333334</v>
       </c>
       <c r="E2">
-        <v>757.8399999999999</v>
+        <v>841.8200000000002</v>
       </c>
       <c r="F2">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
       </c>
       <c r="C3">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D3">
-        <v>147.816</v>
+        <v>139.1066666666667</v>
       </c>
       <c r="E3">
-        <v>739.0800000000002</v>
+        <v>834.6399999999999</v>
       </c>
       <c r="F3">
-        <v>98</v>
+        <v>98.3</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C4">
-        <v>0.8</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D4">
-        <v>138.468</v>
+        <v>132.5833333333333</v>
       </c>
       <c r="E4">
-        <v>692.34</v>
+        <v>795.5</v>
       </c>
       <c r="F4">
-        <v>96.5</v>
+        <v>97.5</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>65</v>
       </c>
       <c r="C5">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D5">
-        <v>139.08</v>
+        <v>133.5233333333333</v>
       </c>
       <c r="E5">
-        <v>695.4</v>
+        <v>801.14</v>
       </c>
       <c r="F5">
-        <v>92.30000000000001</v>
+        <v>96.89999999999999</v>
       </c>
       <c r="G5">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C6">
-        <v>0.8</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D6">
-        <v>130.768</v>
+        <v>132.12</v>
       </c>
       <c r="E6">
-        <v>653.84</v>
+        <v>792.72</v>
       </c>
       <c r="F6">
-        <v>91.2</v>
+        <v>96.5</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B7" t="s">
         <v>65</v>
       </c>
       <c r="C7">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D7">
-        <v>130.692</v>
+        <v>118.4266666666667</v>
       </c>
       <c r="E7">
-        <v>653.46</v>
+        <v>710.5600000000001</v>
       </c>
       <c r="F7">
-        <v>74.7</v>
+        <v>60.7</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2923,25 +2979,25 @@
         <v>66</v>
       </c>
       <c r="C8">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="D8">
-        <v>127.504</v>
+        <v>121.72</v>
       </c>
       <c r="E8">
-        <v>637.52</v>
+        <v>730.3199999999999</v>
       </c>
       <c r="F8">
-        <v>34</v>
+        <v>46.6</v>
       </c>
       <c r="G8">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2952,83 +3008,83 @@
         <v>67</v>
       </c>
       <c r="C9">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="D9">
-        <v>125.496</v>
+        <v>114.72</v>
       </c>
       <c r="E9">
-        <v>627.48</v>
+        <v>688.3200000000001</v>
       </c>
       <c r="F9">
-        <v>12</v>
+        <v>4.399999999999999</v>
       </c>
       <c r="G9">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="H9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10" t="s">
         <v>67</v>
       </c>
       <c r="C10">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="D10">
-        <v>107.752</v>
+        <v>92.66666666666667</v>
       </c>
       <c r="E10">
-        <v>538.76</v>
+        <v>556</v>
       </c>
       <c r="F10">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="G10">
-        <v>6.3</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="D11">
-        <v>94.10400000000001</v>
+        <v>101.6066666666667</v>
       </c>
       <c r="E11">
-        <v>470.52</v>
+        <v>609.64</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G11">
-        <v>92.60000000000001</v>
+        <v>21.4</v>
       </c>
       <c r="H11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -3046,16 +3102,16 @@
         <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3066,16 +3122,16 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3083,19 +3139,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
         <v>54</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3103,16 +3159,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
         <v>89</v>
@@ -3123,19 +3179,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3143,19 +3199,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3163,19 +3219,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D7">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3183,19 +3239,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D8">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3203,19 +3259,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D9">
-        <v>-4</v>
+        <v>-12</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3229,13 +3285,13 @@
         <v>47</v>
       </c>
       <c r="D10">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3246,16 +3302,16 @@
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D11">
-        <v>-17</v>
+        <v>-19</v>
       </c>
       <c r="E11" t="s">
         <v>14</v>
       </c>
       <c r="F11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -3265,257 +3321,290 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
+      </c>
+      <c r="D2">
+        <v>16</v>
+      </c>
+      <c r="E2">
+        <v>20</v>
+      </c>
+      <c r="F2">
+        <v>19</v>
+      </c>
+      <c r="G2">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>-7</v>
+      </c>
+      <c r="C3">
+        <v>-8</v>
+      </c>
+      <c r="D3">
+        <v>-5</v>
+      </c>
+      <c r="E3">
+        <v>-4</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>11</v>
+      </c>
+      <c r="H3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4">
         <v>4</v>
       </c>
-      <c r="C2">
-        <v>8</v>
-      </c>
-      <c r="D2">
-        <v>14</v>
-      </c>
-      <c r="E2">
-        <v>19</v>
-      </c>
-      <c r="F2">
-        <v>18</v>
-      </c>
-      <c r="G2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="1" t="s">
+      <c r="C4">
+        <v>-4</v>
+      </c>
+      <c r="D4">
         <v>1</v>
       </c>
-      <c r="B3">
-        <v>5</v>
-      </c>
-      <c r="C3">
-        <v>-4</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>10</v>
-      </c>
-      <c r="G3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>6</v>
-      </c>
-      <c r="D4">
-        <v>5</v>
-      </c>
       <c r="E4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <v>6</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4">
+        <v>10</v>
+      </c>
+      <c r="H4" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C5">
         <v>5</v>
       </c>
       <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>8</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>-5</v>
+      </c>
+      <c r="G6">
         <v>4</v>
       </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
+      <c r="H6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+      <c r="D7">
+        <v>4</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>4</v>
+      </c>
+      <c r="G7">
         <v>2</v>
       </c>
-      <c r="G5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="1" t="s">
+      <c r="H7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B6">
+      <c r="B8">
         <v>-2</v>
       </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>8</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <v>-1</v>
-      </c>
-      <c r="G6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>-8</v>
-      </c>
-      <c r="C7">
-        <v>-8</v>
-      </c>
-      <c r="D7">
-        <v>-5</v>
-      </c>
-      <c r="E7">
-        <v>-4</v>
-      </c>
-      <c r="F7">
-        <v>-2</v>
-      </c>
-      <c r="G7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
       <c r="C8">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>-11</v>
+        <v>7</v>
       </c>
       <c r="E8">
-        <v>-8</v>
+        <v>7</v>
       </c>
       <c r="F8">
         <v>-2</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8">
+        <v>-6</v>
+      </c>
+      <c r="H8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>-4</v>
+      </c>
+      <c r="D9">
+        <v>-13</v>
+      </c>
+      <c r="E9">
+        <v>-11</v>
+      </c>
+      <c r="F9">
+        <v>-7</v>
+      </c>
+      <c r="G9">
+        <v>-12</v>
+      </c>
+      <c r="H9" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>4</v>
-      </c>
-      <c r="C9">
-        <v>8</v>
-      </c>
-      <c r="D9">
-        <v>5</v>
-      </c>
-      <c r="E9">
-        <v>4</v>
-      </c>
-      <c r="F9">
-        <v>-4</v>
-      </c>
-      <c r="G9" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B10">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="C10">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="D10">
         <v>-10</v>
       </c>
       <c r="E10">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="F10">
-        <v>-10</v>
-      </c>
-      <c r="G10" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>-8</v>
+      </c>
+      <c r="G10">
+        <v>-16</v>
+      </c>
+      <c r="H10" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11">
+        <v>-7</v>
+      </c>
+      <c r="D11">
         <v>-10</v>
       </c>
-      <c r="D11">
-        <v>-13</v>
-      </c>
       <c r="E11">
-        <v>-17</v>
+        <v>-14</v>
       </c>
       <c r="F11">
-        <v>-17</v>
-      </c>
-      <c r="G11" t="s">
-        <v>96</v>
+        <v>-14</v>
+      </c>
+      <c r="G11">
+        <v>-19</v>
+      </c>
+      <c r="H11" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/The Goofy Goobers 2026.xlsx
+++ b/data/leagues/The Goofy Goobers 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="112">
   <si>
     <t>Rice Rice Baby</t>
   </si>
@@ -55,22 +55,25 @@
     <t>Delco Football Team</t>
   </si>
   <si>
-    <t>4-2-0</t>
-  </si>
-  <si>
-    <t>5-1-0</t>
-  </si>
-  <si>
-    <t>3-3-0</t>
-  </si>
-  <si>
-    <t>2-4-0</t>
-  </si>
-  <si>
-    <t>1-5-0</t>
-  </si>
-  <si>
-    <t>0-6-0</t>
+    <t>4-3-0</t>
+  </si>
+  <si>
+    <t>6-1-0</t>
+  </si>
+  <si>
+    <t>3-4-0</t>
+  </si>
+  <si>
+    <t>2-5-0</t>
+  </si>
+  <si>
+    <t>5-2-0</t>
+  </si>
+  <si>
+    <t>1-6-0</t>
+  </si>
+  <si>
+    <t>0-7-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -145,6 +148,9 @@
     <t>Week_7</t>
   </si>
   <si>
+    <t>Week_8</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -166,30 +172,30 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>Samuel DiPasqua</t>
+  </si>
+  <si>
+    <t>Derrick Edmiston</t>
+  </si>
+  <si>
     <t>Marvin Ta</t>
   </si>
   <si>
-    <t>Samuel DiPasqua</t>
+    <t>Horatio Kneepads</t>
+  </si>
+  <si>
+    <t>Prahlad Singh</t>
+  </si>
+  <si>
+    <t>Stan Yu</t>
+  </si>
+  <si>
+    <t>Bridget Cashel</t>
   </si>
   <si>
     <t>Anthony Rizzo</t>
   </si>
   <si>
-    <t>Stan Yu</t>
-  </si>
-  <si>
-    <t>Derrick Edmiston</t>
-  </si>
-  <si>
-    <t>Prahlad Singh</t>
-  </si>
-  <si>
-    <t>Horatio Kneepads</t>
-  </si>
-  <si>
-    <t>Bridget Cashel</t>
-  </si>
-  <si>
     <t>Andrew Bock</t>
   </si>
   <si>
@@ -220,43 +226,46 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>4-2</t>
-  </si>
-  <si>
-    <t>3-3</t>
-  </si>
-  <si>
-    <t>1-5</t>
-  </si>
-  <si>
-    <t>9.6-4.4-0.1</t>
-  </si>
-  <si>
-    <t>9.6-4.3-0.1</t>
-  </si>
-  <si>
-    <t>9.0-4.9-0.1</t>
-  </si>
-  <si>
-    <t>9.1-4.8-0.1</t>
-  </si>
-  <si>
-    <t>8.8-5.1-0.1</t>
-  </si>
-  <si>
-    <t>7.2-6.7-0.1</t>
-  </si>
-  <si>
-    <t>6.6-7.3-0.1</t>
-  </si>
-  <si>
-    <t>4.4-9.5-0.1</t>
-  </si>
-  <si>
-    <t>2.2-11.7-0.1</t>
-  </si>
-  <si>
-    <t>3.1-10.8-0.1</t>
+    <t>5-2</t>
+  </si>
+  <si>
+    <t>4-3</t>
+  </si>
+  <si>
+    <t>1-6</t>
+  </si>
+  <si>
+    <t>2-5</t>
+  </si>
+  <si>
+    <t>10.2-3.7-0.1</t>
+  </si>
+  <si>
+    <t>10.1-3.8-0.1</t>
+  </si>
+  <si>
+    <t>9.1-4.9-0.1</t>
+  </si>
+  <si>
+    <t>8.4-5.5-0.1</t>
+  </si>
+  <si>
+    <t>8.0-6.0-0.1</t>
+  </si>
+  <si>
+    <t>7.1-6.8-0.1</t>
+  </si>
+  <si>
+    <t>3.9-10.0-0.1</t>
+  </si>
+  <si>
+    <t>3.9-10.0</t>
+  </si>
+  <si>
+    <t>1.8-12.1-0.1</t>
+  </si>
+  <si>
+    <t>11-3</t>
   </si>
   <si>
     <t>10-4</t>
@@ -265,6 +274,9 @@
     <t>9-5</t>
   </si>
   <si>
+    <t>8-6</t>
+  </si>
+  <si>
     <t>7-7</t>
   </si>
   <si>
@@ -274,9 +286,6 @@
     <t>2-12</t>
   </si>
   <si>
-    <t>3-11</t>
-  </si>
-  <si>
     <t>Owners</t>
   </si>
   <si>
@@ -286,30 +295,30 @@
     <t>Change From Last Week</t>
   </si>
   <si>
-    <t>↑1</t>
-  </si>
-  <si>
-    <t>↑11</t>
-  </si>
-  <si>
-    <t>↑4</t>
-  </si>
-  <si>
-    <t>↓2</t>
-  </si>
-  <si>
-    <t>↑9</t>
+    <t>↑8</t>
+  </si>
+  <si>
+    <t>↑7</t>
+  </si>
+  <si>
+    <t>↑5</t>
+  </si>
+  <si>
+    <t>↓7</t>
+  </si>
+  <si>
+    <t>↓3</t>
   </si>
   <si>
     <t>↓4</t>
   </si>
   <si>
+    <t>↓1</t>
+  </si>
+  <si>
     <t>↓5</t>
   </si>
   <si>
-    <t>↓8</t>
-  </si>
-  <si>
     <t>Week 1</t>
   </si>
   <si>
@@ -326,6 +335,9 @@
   </si>
   <si>
     <t>Week 6</t>
+  </si>
+  <si>
+    <t>Week 7</t>
   </si>
   <si>
     <t>Week</t>
@@ -753,10 +765,10 @@
         <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
         <v>13</v>
@@ -765,13 +777,13 @@
         <v>12</v>
       </c>
       <c r="I2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -782,31 +794,31 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G3" t="s">
         <v>11</v>
       </c>
       <c r="H3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -817,31 +829,31 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s">
         <v>15</v>
       </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
       <c r="G4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" t="s">
         <v>15</v>
-      </c>
-      <c r="H4" t="s">
-        <v>14</v>
       </c>
       <c r="I4" t="s">
         <v>13</v>
       </c>
       <c r="J4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -852,31 +864,31 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
         <v>13</v>
       </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>14</v>
-      </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H5" t="s">
         <v>13</v>
       </c>
       <c r="I5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -893,10 +905,10 @@
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G6" t="s">
         <v>12</v>
@@ -905,13 +917,13 @@
         <v>12</v>
       </c>
       <c r="I6" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J6" t="s">
         <v>12</v>
       </c>
       <c r="K6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -922,19 +934,19 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F7" t="s">
         <v>11</v>
       </c>
       <c r="G7" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H7" t="s">
         <v>11</v>
@@ -943,7 +955,7 @@
         <v>11</v>
       </c>
       <c r="J7" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K7" t="s">
         <v>11</v>
@@ -957,13 +969,13 @@
         <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F8" t="s">
         <v>11</v>
@@ -975,13 +987,13 @@
         <v>10</v>
       </c>
       <c r="I8" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J8" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -989,7 +1001,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -998,25 +1010,25 @@
         <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G9" t="s">
         <v>10</v>
       </c>
       <c r="H9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I9" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J9" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1030,13 +1042,13 @@
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" t="s">
         <v>13</v>
-      </c>
-      <c r="F10" t="s">
-        <v>14</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -1048,7 +1060,7 @@
         <v>12</v>
       </c>
       <c r="J10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K10" t="s">
         <v>13</v>
@@ -1068,7 +1080,7 @@
         <v>13</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F11" t="s">
         <v>12</v>
@@ -1077,13 +1089,13 @@
         <v>10</v>
       </c>
       <c r="H11" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I11" t="s">
         <v>10</v>
       </c>
       <c r="J11" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K11" t="s">
         <v>10</v>
@@ -1101,25 +1113,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1231,25 +1243,25 @@
         <v>4</v>
       </c>
       <c r="B6">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
         <v>4</v>
-      </c>
-      <c r="C6" t="s">
-        <v>1</v>
       </c>
       <c r="D6" t="s">
         <v>9</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="F6">
-        <v>-4</v>
+        <v>4</v>
       </c>
       <c r="G6">
+        <v>6</v>
+      </c>
+      <c r="H6" t="s">
         <v>4</v>
-      </c>
-      <c r="H6" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1283,25 +1295,25 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E8">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1309,25 +1321,25 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D9" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9">
-        <v>-16</v>
+        <v>-5</v>
       </c>
       <c r="F9">
-        <v>-19</v>
+        <v>-2</v>
       </c>
       <c r="G9">
         <v>3</v>
       </c>
       <c r="H9" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1335,25 +1347,25 @@
         <v>8</v>
       </c>
       <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E10">
+        <v>-16</v>
+      </c>
+      <c r="F10">
+        <v>-19</v>
+      </c>
+      <c r="G10">
         <v>3</v>
       </c>
-      <c r="C10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10">
-        <v>5</v>
-      </c>
-      <c r="F10">
-        <v>4</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
       <c r="H10" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1368,13 +1380,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1382,13 +1394,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2">
         <v>3</v>
       </c>
-      <c r="C2">
-        <v>2.2</v>
-      </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1396,13 +1408,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1410,13 +1422,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1424,13 +1436,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1438,13 +1450,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1452,13 +1464,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1466,10 +1478,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -1483,7 +1495,7 @@
         <v>6</v>
       </c>
       <c r="C9">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
@@ -1494,10 +1506,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="D10" t="s">
         <v>10</v>
@@ -1508,13 +1520,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C11">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1529,16 +1541,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1549,13 +1561,13 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="D2">
-        <v>0.5</v>
+        <v>0.4000000000000004</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1566,13 +1578,13 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="D3">
-        <v>-0.1000000000000001</v>
+        <v>-0.09999999999999964</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1583,10 +1595,10 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="D4">
-        <v>-0.1000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -1600,13 +1612,13 @@
         <v>7</v>
       </c>
       <c r="C5">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="D5">
-        <v>-0.2000000000000002</v>
+        <v>-0.7000000000000002</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1617,10 +1629,10 @@
         <v>9</v>
       </c>
       <c r="C6">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="D6">
-        <v>-0.2999999999999998</v>
+        <v>-0.2000000000000002</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -1634,13 +1646,13 @@
         <v>4</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>-0.6000000000000001</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1651,10 +1663,10 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="D8">
-        <v>-1.5</v>
+        <v>-1</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -1665,16 +1677,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C9">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="D9">
-        <v>0.8999999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1682,16 +1694,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C10">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="D10">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1708,7 +1720,7 @@
         <v>0.1000000000000001</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1723,69 +1735,69 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B2">
-        <v>32.1</v>
+        <v>41</v>
       </c>
       <c r="C2">
-        <v>24.1</v>
+        <v>34.6</v>
       </c>
       <c r="D2">
-        <v>17.5</v>
+        <v>14.6</v>
       </c>
       <c r="E2">
-        <v>12.4</v>
+        <v>6.4</v>
       </c>
       <c r="F2">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="G2">
-        <v>4.3</v>
+        <v>0.9</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1794,36 +1806,36 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>98.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B3">
-        <v>30.9</v>
+        <v>42.9</v>
       </c>
       <c r="C3">
-        <v>24.2</v>
+        <v>33</v>
       </c>
       <c r="D3">
-        <v>18.4</v>
+        <v>14.1</v>
       </c>
       <c r="E3">
-        <v>12.5</v>
+        <v>6.1</v>
       </c>
       <c r="F3">
-        <v>7.6</v>
+        <v>3.1</v>
       </c>
       <c r="G3">
-        <v>4.7</v>
+        <v>0.6</v>
       </c>
       <c r="H3">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="I3">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1832,36 +1844,36 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>98.3</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4">
-        <v>11</v>
+        <v>8.9</v>
       </c>
       <c r="C4">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="D4">
-        <v>21.4</v>
+        <v>28.3</v>
       </c>
       <c r="E4">
-        <v>20.5</v>
+        <v>23.7</v>
       </c>
       <c r="F4">
-        <v>19.5</v>
+        <v>12.2</v>
       </c>
       <c r="G4">
-        <v>8.9</v>
+        <v>7.7</v>
       </c>
       <c r="H4">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="I4">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1870,74 +1882,74 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>97.5</v>
+        <v>97.09999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5">
-        <v>14.1</v>
+        <v>4.8</v>
       </c>
       <c r="C5">
-        <v>17.8</v>
+        <v>9</v>
       </c>
       <c r="D5">
-        <v>20.9</v>
+        <v>21.5</v>
       </c>
       <c r="E5">
-        <v>21.1</v>
+        <v>27.7</v>
       </c>
       <c r="F5">
-        <v>16.8</v>
+        <v>20.8</v>
       </c>
       <c r="G5">
-        <v>6.2</v>
+        <v>11.1</v>
       </c>
       <c r="H5">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="I5">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="J5">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>96.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B6">
-        <v>10.9</v>
+        <v>1.5</v>
       </c>
       <c r="C6">
-        <v>14</v>
+        <v>4.6</v>
       </c>
       <c r="D6">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E6">
-        <v>21.9</v>
+        <v>19.5</v>
       </c>
       <c r="F6">
-        <v>20.8</v>
+        <v>28.9</v>
       </c>
       <c r="G6">
-        <v>12.9</v>
+        <v>20.3</v>
       </c>
       <c r="H6">
-        <v>3.3</v>
+        <v>10.2</v>
       </c>
       <c r="I6">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1946,83 +1958,83 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>96.5</v>
+        <v>88.7</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B7">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="C7">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="D7">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="E7">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
       <c r="F7">
-        <v>14.7</v>
+        <v>16.6</v>
       </c>
       <c r="G7">
         <v>31.8</v>
       </c>
       <c r="H7">
-        <v>29.9</v>
+        <v>34.1</v>
       </c>
       <c r="I7">
-        <v>8.6</v>
+        <v>5.5</v>
       </c>
       <c r="J7">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>60.7</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="1" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B8">
         <v>0.4</v>
       </c>
       <c r="C8">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="D8">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="E8">
-        <v>3.4</v>
+        <v>9.4</v>
       </c>
       <c r="F8">
-        <v>11.2</v>
+        <v>15.5</v>
       </c>
       <c r="G8">
-        <v>27.8</v>
+        <v>25.7</v>
       </c>
       <c r="H8">
-        <v>41.2</v>
+        <v>37.3</v>
       </c>
       <c r="I8">
-        <v>11.6</v>
+        <v>5</v>
       </c>
       <c r="J8">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>46.6</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -2039,33 +2051,33 @@
         <v>0</v>
       </c>
       <c r="E9">
+        <v>0.1</v>
+      </c>
+      <c r="F9">
         <v>0.3</v>
       </c>
-      <c r="F9">
-        <v>0.9</v>
-      </c>
       <c r="G9">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="H9">
-        <v>15</v>
+        <v>6.9</v>
       </c>
       <c r="I9">
-        <v>58.8</v>
+        <v>49.9</v>
       </c>
       <c r="J9">
-        <v>17.6</v>
+        <v>36.2</v>
       </c>
       <c r="K9">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="L9">
-        <v>4.4</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2080,30 +2092,30 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G10">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="H10">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="I10">
-        <v>3.9</v>
+        <v>37.3</v>
       </c>
       <c r="J10">
-        <v>21.1</v>
+        <v>54.1</v>
       </c>
       <c r="K10">
-        <v>74.40000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="L10">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2121,22 +2133,22 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>16.3</v>
+        <v>0.7</v>
       </c>
       <c r="J11">
-        <v>59.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="K11">
-        <v>21.4</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="L11">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2146,38 +2158,41 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>40</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B2">
-        <v>99.2</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -2189,16 +2204,19 @@
         <v>100</v>
       </c>
       <c r="F2">
-        <v>99.5</v>
+        <v>99.8</v>
       </c>
       <c r="G2">
-        <v>98.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="H2">
-        <v>99.2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>99.7</v>
+      </c>
+      <c r="I2">
+        <v>99.90000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -2206,155 +2224,173 @@
         <v>100</v>
       </c>
       <c r="C3">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="D3">
-        <v>99.8</v>
+        <v>99.7</v>
       </c>
       <c r="E3">
         <v>98.8</v>
       </c>
       <c r="F3">
-        <v>97.7</v>
+        <v>97.5</v>
       </c>
       <c r="G3">
         <v>98.09999999999999</v>
       </c>
       <c r="H3">
-        <v>98.40000000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>99.7</v>
+      </c>
+      <c r="I3">
+        <v>99.8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B4">
-        <v>98.2</v>
+        <v>97.39999999999999</v>
       </c>
       <c r="C4">
         <v>100</v>
       </c>
       <c r="D4">
-        <v>99.3</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="E4">
-        <v>99.90000000000001</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="F4">
-        <v>97.8</v>
+        <v>97.3</v>
       </c>
       <c r="G4">
-        <v>95.59999999999999</v>
+        <v>95.89999999999999</v>
       </c>
       <c r="H4">
-        <v>95.89999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>98.5</v>
+      </c>
+      <c r="I4">
+        <v>97.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B5">
-        <v>62</v>
+        <v>63.2</v>
       </c>
       <c r="C5">
-        <v>93.89999999999999</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="D5">
-        <v>97.7</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="E5">
-        <v>99.7</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="F5">
+        <v>91.3</v>
+      </c>
+      <c r="G5">
+        <v>95.3</v>
+      </c>
+      <c r="H5">
         <v>92.30000000000001</v>
       </c>
-      <c r="G5">
-        <v>95</v>
-      </c>
-      <c r="H5">
-        <v>95.59999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B6">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>46.40000000000001</v>
+        <v>45.1</v>
       </c>
       <c r="D6">
-        <v>31.8</v>
+        <v>28.4</v>
       </c>
       <c r="E6">
-        <v>66.7</v>
+        <v>65.3</v>
       </c>
       <c r="F6">
-        <v>73.7</v>
+        <v>75.2</v>
       </c>
       <c r="G6">
-        <v>95.5</v>
+        <v>94.39999999999999</v>
       </c>
       <c r="H6">
-        <v>95.59999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>89.2</v>
+      </c>
+      <c r="I6">
+        <v>87.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B7">
-        <v>61.2</v>
+        <v>31.5</v>
       </c>
       <c r="C7">
-        <v>32</v>
+        <v>44.5</v>
       </c>
       <c r="D7">
-        <v>38</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="E7">
-        <v>88.7</v>
+        <v>17.3</v>
       </c>
       <c r="F7">
-        <v>84.89999999999999</v>
+        <v>44.9</v>
       </c>
       <c r="G7">
-        <v>65.10000000000001</v>
+        <v>49.7</v>
       </c>
       <c r="H7">
-        <v>60.6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>59.4</v>
+      </c>
+      <c r="I7">
+        <v>60.9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B8">
-        <v>29.8</v>
+        <v>58.7</v>
       </c>
       <c r="C8">
-        <v>40.3</v>
+        <v>32.9</v>
       </c>
       <c r="D8">
-        <v>71.7</v>
+        <v>37.4</v>
       </c>
       <c r="E8">
-        <v>16.5</v>
+        <v>90.10000000000001</v>
       </c>
       <c r="F8">
-        <v>42.6</v>
+        <v>81.5</v>
       </c>
       <c r="G8">
-        <v>48.4</v>
+        <v>64.5</v>
       </c>
       <c r="H8">
-        <v>50.8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>57.2</v>
+      </c>
+      <c r="I8">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -2362,51 +2398,57 @@
         <v>99.90000000000001</v>
       </c>
       <c r="C9">
-        <v>83.8</v>
+        <v>79.5</v>
       </c>
       <c r="D9">
-        <v>22.4</v>
+        <v>21.8</v>
       </c>
       <c r="E9">
-        <v>9.199999999999999</v>
+        <v>11.1</v>
       </c>
       <c r="F9">
-        <v>11.2</v>
+        <v>11.8</v>
       </c>
       <c r="G9">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="H9">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>2.6</v>
+      </c>
+      <c r="I9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B10">
+        <v>0.3</v>
+      </c>
+      <c r="C10">
+        <v>1.5</v>
+      </c>
+      <c r="D10">
+        <v>39.90000000000001</v>
+      </c>
+      <c r="E10">
+        <v>18.4</v>
+      </c>
+      <c r="F10">
         <v>0.7000000000000001</v>
       </c>
-      <c r="C10">
-        <v>2.5</v>
-      </c>
-      <c r="D10">
-        <v>39.3</v>
-      </c>
-      <c r="E10">
-        <v>20.4</v>
-      </c>
-      <c r="F10">
-        <v>0.3</v>
-      </c>
       <c r="G10">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="H10">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>1.4</v>
+      </c>
+      <c r="I10">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
         <v>2</v>
       </c>
@@ -2414,13 +2456,13 @@
         <v>44.4</v>
       </c>
       <c r="C11">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E11">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -2429,6 +2471,9 @@
         <v>0</v>
       </c>
       <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
         <v>0</v>
       </c>
     </row>
@@ -2444,28 +2489,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2473,28 +2518,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D2">
-        <v>118.43</v>
+        <v>91.77</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>126.96</v>
+        <v>128.41</v>
       </c>
       <c r="G2">
-        <v>0.521</v>
+        <v>0.571</v>
       </c>
       <c r="H2">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="I2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2502,28 +2547,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D3">
-        <v>92.67</v>
+        <v>105.66</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F3">
-        <v>126.96</v>
+        <v>128.46</v>
       </c>
       <c r="G3">
-        <v>0.521</v>
+        <v>0.571</v>
       </c>
       <c r="H3">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="I3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2531,28 +2576,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D4">
-        <v>132.12</v>
+        <v>119.16</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4">
-        <v>122.49</v>
+        <v>123.4</v>
       </c>
       <c r="G4">
-        <v>0.521</v>
+        <v>0.51</v>
       </c>
       <c r="H4">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2560,28 +2605,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D5">
-        <v>114.72</v>
+        <v>129.92</v>
       </c>
       <c r="E5" t="s">
         <v>14</v>
       </c>
       <c r="F5">
-        <v>122.49</v>
+        <v>120.87</v>
       </c>
       <c r="G5">
-        <v>0.521</v>
+        <v>0.51</v>
       </c>
       <c r="H5">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2589,28 +2634,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D6">
-        <v>101.61</v>
+        <v>118.78</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>125.43</v>
+        <v>123.44</v>
       </c>
       <c r="G6">
-        <v>0.542</v>
+        <v>0.51</v>
       </c>
       <c r="H6">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2618,28 +2663,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D7">
-        <v>121.72</v>
+        <v>112.47</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F7">
-        <v>125.43</v>
+        <v>120.19</v>
       </c>
       <c r="G7">
-        <v>0.542</v>
+        <v>0.51</v>
       </c>
       <c r="H7">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2647,28 +2692,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8">
+        <v>126.93</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8">
+        <v>119.97</v>
+      </c>
+      <c r="G8">
+        <v>0.449</v>
+      </c>
+      <c r="H8">
+        <v>-0.3</v>
+      </c>
+      <c r="I8">
         <v>7</v>
-      </c>
-      <c r="C8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D8">
-        <v>133.52</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8">
-        <v>120.08</v>
-      </c>
-      <c r="G8">
-        <v>0.458</v>
-      </c>
-      <c r="H8">
-        <v>-1.9</v>
-      </c>
-      <c r="I8">
-        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2676,28 +2721,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D9">
-        <v>132.58</v>
+        <v>131.73</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9">
-        <v>120.08</v>
+        <v>118.99</v>
       </c>
       <c r="G9">
-        <v>0.458</v>
+        <v>0.51</v>
       </c>
       <c r="H9">
-        <v>-1.9</v>
+        <v>-3</v>
       </c>
       <c r="I9">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2708,25 +2753,25 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D10">
-        <v>140.3</v>
+        <v>140.71</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F10">
-        <v>118.42</v>
+        <v>116.75</v>
       </c>
       <c r="G10">
-        <v>0.458</v>
+        <v>0.429</v>
       </c>
       <c r="H10">
-        <v>-3.8</v>
+        <v>-4.7</v>
       </c>
       <c r="I10">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2737,25 +2782,25 @@
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D11">
-        <v>139.11</v>
+        <v>138.31</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F11">
-        <v>118.42</v>
+        <v>114.96</v>
       </c>
       <c r="G11">
-        <v>0.458</v>
+        <v>0.429</v>
       </c>
       <c r="H11">
-        <v>-3.8</v>
+        <v>-7.9</v>
       </c>
       <c r="I11">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2770,234 +2815,234 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C2">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D2">
-        <v>140.3033333333334</v>
+        <v>138.3114285714285</v>
       </c>
       <c r="E2">
-        <v>841.8200000000002</v>
+        <v>968.1799999999998</v>
       </c>
       <c r="F2">
-        <v>98.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="I2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C3">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D3">
-        <v>139.1066666666667</v>
+        <v>140.7057142857143</v>
       </c>
       <c r="E3">
-        <v>834.6399999999999</v>
+        <v>984.9400000000002</v>
       </c>
       <c r="F3">
-        <v>98.3</v>
+        <v>99.8</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C4">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D4">
-        <v>132.5833333333333</v>
+        <v>129.9228571428571</v>
       </c>
       <c r="E4">
-        <v>795.5</v>
+        <v>909.46</v>
       </c>
       <c r="F4">
-        <v>97.5</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I4" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C5">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D5">
-        <v>133.5233333333333</v>
+        <v>131.7285714285714</v>
       </c>
       <c r="E5">
-        <v>801.14</v>
+        <v>922.1</v>
       </c>
       <c r="F5">
-        <v>96.89999999999999</v>
+        <v>94.89999999999999</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C6">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D6">
-        <v>132.12</v>
+        <v>126.9314285714286</v>
       </c>
       <c r="E6">
-        <v>792.72</v>
+        <v>888.52</v>
       </c>
       <c r="F6">
-        <v>96.5</v>
+        <v>88.7</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I6" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C7">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D7">
-        <v>118.4266666666667</v>
+        <v>118.7771428571428</v>
       </c>
       <c r="E7">
-        <v>710.5600000000001</v>
+        <v>831.4399999999999</v>
       </c>
       <c r="F7">
-        <v>60.7</v>
+        <v>59.9</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I7" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C8">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D8">
-        <v>121.72</v>
+        <v>119.1628571428572</v>
       </c>
       <c r="E8">
-        <v>730.3199999999999</v>
+        <v>834.1400000000001</v>
       </c>
       <c r="F8">
-        <v>46.6</v>
+        <v>57.2</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I8" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -3005,86 +3050,86 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C9">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D9">
-        <v>114.72</v>
+        <v>112.4685714285714</v>
       </c>
       <c r="E9">
-        <v>688.3200000000001</v>
+        <v>787.2800000000001</v>
       </c>
       <c r="F9">
-        <v>4.399999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="G9">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="H9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I9" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C10">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D10">
-        <v>92.66666666666667</v>
+        <v>105.6628571428571</v>
       </c>
       <c r="E10">
-        <v>556</v>
+        <v>739.64</v>
       </c>
       <c r="F10">
-        <v>0.1</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="G10">
-        <v>74.40000000000001</v>
+        <v>4.100000000000001</v>
       </c>
       <c r="H10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I10" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C11">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D11">
-        <v>101.6066666666667</v>
+        <v>91.77142857142857</v>
       </c>
       <c r="E11">
-        <v>609.64</v>
+        <v>642.4</v>
       </c>
       <c r="F11">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>21.4</v>
+        <v>90.60000000000001</v>
       </c>
       <c r="H11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I11" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -3099,19 +3144,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3122,16 +3167,16 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3139,19 +3184,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3159,19 +3204,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3179,19 +3224,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3202,16 +3247,16 @@
         <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3222,16 +3267,16 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3242,16 +3287,16 @@
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3259,19 +3304,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D9">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3279,19 +3324,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D10">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3302,16 +3347,16 @@
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D11">
-        <v>-19</v>
+        <v>-23</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F11" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -3321,33 +3366,36 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>104</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -3369,89 +3417,101 @@
       <c r="G2">
         <v>20</v>
       </c>
-      <c r="H2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="H2">
+        <v>28</v>
+      </c>
+      <c r="I2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>-4</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>6</v>
+      </c>
+      <c r="G3">
+        <v>10</v>
+      </c>
+      <c r="H3">
+        <v>17</v>
+      </c>
+      <c r="I3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>7</v>
+      </c>
+      <c r="F4">
+        <v>8</v>
+      </c>
+      <c r="G4">
+        <v>6</v>
+      </c>
+      <c r="H4">
+        <v>11</v>
+      </c>
+      <c r="I4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3">
+      <c r="B5">
         <v>-7</v>
       </c>
-      <c r="C3">
+      <c r="C5">
         <v>-8</v>
       </c>
-      <c r="D3">
+      <c r="D5">
         <v>-5</v>
       </c>
-      <c r="E3">
+      <c r="E5">
         <v>-4</v>
       </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
         <v>11</v>
       </c>
-      <c r="H3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4">
+      <c r="H5">
         <v>4</v>
       </c>
-      <c r="C4">
-        <v>-4</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>6</v>
-      </c>
-      <c r="G4">
-        <v>10</v>
-      </c>
-      <c r="H4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-      <c r="F5">
-        <v>8</v>
-      </c>
-      <c r="G5">
-        <v>6</v>
-      </c>
-      <c r="H5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -3473,11 +3533,14 @@
       <c r="G6">
         <v>4</v>
       </c>
-      <c r="H6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -3499,11 +3562,14 @@
       <c r="G7">
         <v>2</v>
       </c>
-      <c r="H7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="H7">
+        <v>-2</v>
+      </c>
+      <c r="I7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
@@ -3525,63 +3591,72 @@
       <c r="G8">
         <v>-6</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8">
+        <v>-7</v>
+      </c>
+      <c r="I8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9">
+        <v>-5</v>
+      </c>
+      <c r="C9">
+        <v>-2</v>
+      </c>
+      <c r="D9">
+        <v>-10</v>
+      </c>
+      <c r="E9">
+        <v>-10</v>
+      </c>
+      <c r="F9">
+        <v>-8</v>
+      </c>
+      <c r="G9">
+        <v>-16</v>
+      </c>
+      <c r="H9">
+        <v>-11</v>
+      </c>
+      <c r="I9" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="1" t="s">
+    <row r="10" spans="1:9">
+      <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
         <v>-4</v>
       </c>
-      <c r="D9">
+      <c r="D10">
         <v>-13</v>
       </c>
-      <c r="E9">
+      <c r="E10">
         <v>-11</v>
       </c>
-      <c r="F9">
+      <c r="F10">
         <v>-7</v>
       </c>
-      <c r="G9">
+      <c r="G10">
         <v>-12</v>
       </c>
-      <c r="H9" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10">
-        <v>-5</v>
-      </c>
-      <c r="C10">
-        <v>-2</v>
-      </c>
-      <c r="D10">
-        <v>-10</v>
-      </c>
-      <c r="E10">
-        <v>-10</v>
-      </c>
-      <c r="F10">
-        <v>-8</v>
-      </c>
-      <c r="G10">
-        <v>-16</v>
-      </c>
-      <c r="H10" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="H10">
+        <v>-17</v>
+      </c>
+      <c r="I10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
         <v>2</v>
       </c>
@@ -3603,8 +3678,11 @@
       <c r="G11">
         <v>-19</v>
       </c>
-      <c r="H11" t="s">
-        <v>93</v>
+      <c r="H11">
+        <v>-23</v>
+      </c>
+      <c r="I11" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/The Goofy Goobers 2026.xlsx
+++ b/data/leagues/The Goofy Goobers 2026.xlsx
@@ -238,34 +238,34 @@
     <t>2-5</t>
   </si>
   <si>
-    <t>10.2-3.7-0.1</t>
-  </si>
-  <si>
-    <t>10.1-3.8-0.1</t>
-  </si>
-  <si>
-    <t>9.1-4.9-0.1</t>
+    <t>10.2-3.8-0.1</t>
+  </si>
+  <si>
+    <t>10.0-3.9-0.1</t>
+  </si>
+  <si>
+    <t>9.2-4.7-0.1</t>
   </si>
   <si>
     <t>8.4-5.5-0.1</t>
   </si>
   <si>
-    <t>8.0-6.0-0.1</t>
+    <t>8.0-5.9-0.1</t>
   </si>
   <si>
     <t>7.1-6.8-0.1</t>
   </si>
   <si>
+    <t>7.0-6.9-0.1</t>
+  </si>
+  <si>
+    <t>3.9-10.0</t>
+  </si>
+  <si>
     <t>3.9-10.0-0.1</t>
   </si>
   <si>
-    <t>3.9-10.0</t>
-  </si>
-  <si>
-    <t>1.8-12.1-0.1</t>
-  </si>
-  <si>
-    <t>11-3</t>
+    <t>1.9-12.1</t>
   </si>
   <si>
     <t>10-4</t>
@@ -1779,19 +1779,19 @@
         <v>41</v>
       </c>
       <c r="C2">
-        <v>34.6</v>
+        <v>32.8</v>
       </c>
       <c r="D2">
-        <v>14.6</v>
+        <v>14.8</v>
       </c>
       <c r="E2">
-        <v>6.4</v>
+        <v>6.9</v>
       </c>
       <c r="F2">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="G2">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1814,25 +1814,25 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>42.9</v>
+        <v>42.7</v>
       </c>
       <c r="C3">
-        <v>33</v>
+        <v>28.5</v>
       </c>
       <c r="D3">
-        <v>14.1</v>
+        <v>17.5</v>
       </c>
       <c r="E3">
-        <v>6.1</v>
+        <v>7.5</v>
       </c>
       <c r="F3">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H3">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1844,7 +1844,7 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1852,25 +1852,25 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>8.9</v>
+        <v>10.9</v>
       </c>
       <c r="C4">
-        <v>16.3</v>
+        <v>19.2</v>
       </c>
       <c r="D4">
-        <v>28.3</v>
+        <v>24.7</v>
       </c>
       <c r="E4">
-        <v>23.7</v>
+        <v>23.2</v>
       </c>
       <c r="F4">
-        <v>12.2</v>
+        <v>13.2</v>
       </c>
       <c r="G4">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="H4">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1882,7 +1882,7 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>97.09999999999999</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1890,37 +1890,37 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="C5">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D5">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="E5">
-        <v>27.7</v>
+        <v>25.7</v>
       </c>
       <c r="F5">
-        <v>20.8</v>
+        <v>19.1</v>
       </c>
       <c r="G5">
-        <v>11.1</v>
+        <v>12</v>
       </c>
       <c r="H5">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="I5">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>94.90000000000001</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1928,37 +1928,37 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="C6">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="D6">
-        <v>13.9</v>
+        <v>15</v>
       </c>
       <c r="E6">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="F6">
-        <v>28.9</v>
+        <v>29.4</v>
       </c>
       <c r="G6">
-        <v>20.3</v>
+        <v>20.8</v>
       </c>
       <c r="H6">
-        <v>10.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>88.7</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1969,34 +1969,34 @@
         <v>0.5</v>
       </c>
       <c r="C7">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="E7">
-        <v>7.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F7">
         <v>16.6</v>
       </c>
       <c r="G7">
-        <v>31.8</v>
+        <v>28.6</v>
       </c>
       <c r="H7">
-        <v>34.1</v>
+        <v>34.5</v>
       </c>
       <c r="I7">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="J7">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>59.9</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -2004,37 +2004,37 @@
         <v>0</v>
       </c>
       <c r="B8">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="C8">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="D8">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="E8">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="F8">
-        <v>15.5</v>
+        <v>15.2</v>
       </c>
       <c r="G8">
-        <v>25.7</v>
+        <v>27.2</v>
       </c>
       <c r="H8">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="I8">
-        <v>5</v>
+        <v>6.3</v>
       </c>
       <c r="J8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>57.2</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -2051,25 +2051,25 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F9">
         <v>0.3</v>
       </c>
       <c r="G9">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="H9">
-        <v>6.9</v>
+        <v>8</v>
       </c>
       <c r="I9">
-        <v>49.9</v>
+        <v>47.8</v>
       </c>
       <c r="J9">
         <v>36.2</v>
       </c>
       <c r="K9">
-        <v>5.3</v>
+        <v>6.3</v>
       </c>
       <c r="L9">
         <v>1.7</v>
@@ -2092,25 +2092,25 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="H10">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="I10">
-        <v>37.3</v>
+        <v>37.7</v>
       </c>
       <c r="J10">
-        <v>54.1</v>
+        <v>53.2</v>
       </c>
       <c r="K10">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="L10">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2136,16 +2136,16 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I11">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J11">
-        <v>8.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="K11">
-        <v>90.59999999999999</v>
+        <v>90</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -2192,7 +2192,7 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>98.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -2204,16 +2204,16 @@
         <v>100</v>
       </c>
       <c r="F2">
+        <v>99.7</v>
+      </c>
+      <c r="G2">
+        <v>98.2</v>
+      </c>
+      <c r="H2">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="I2">
         <v>99.8</v>
-      </c>
-      <c r="G2">
-        <v>98.40000000000001</v>
-      </c>
-      <c r="H2">
-        <v>99.7</v>
-      </c>
-      <c r="I2">
-        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2227,10 +2227,10 @@
         <v>100</v>
       </c>
       <c r="D3">
-        <v>99.7</v>
+        <v>99.8</v>
       </c>
       <c r="E3">
-        <v>98.8</v>
+        <v>98.5</v>
       </c>
       <c r="F3">
         <v>97.5</v>
@@ -2239,10 +2239,10 @@
         <v>98.09999999999999</v>
       </c>
       <c r="H3">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="I3">
         <v>99.7</v>
-      </c>
-      <c r="I3">
-        <v>99.8</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2250,28 +2250,28 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>97.39999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="C4">
         <v>100</v>
       </c>
       <c r="D4">
-        <v>99.40000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="E4">
-        <v>99.59999999999999</v>
+        <v>99.8</v>
       </c>
       <c r="F4">
-        <v>97.3</v>
+        <v>97.2</v>
       </c>
       <c r="G4">
-        <v>95.89999999999999</v>
+        <v>95</v>
       </c>
       <c r="H4">
-        <v>98.5</v>
+        <v>97.5</v>
       </c>
       <c r="I4">
-        <v>97.2</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2279,28 +2279,28 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>63.2</v>
+        <v>61.4</v>
       </c>
       <c r="C5">
-        <v>95.09999999999999</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="D5">
-        <v>98.59999999999999</v>
+        <v>97.89999999999999</v>
       </c>
       <c r="E5">
-        <v>99.40000000000001</v>
+        <v>99.7</v>
       </c>
       <c r="F5">
-        <v>91.3</v>
+        <v>92.30000000000001</v>
       </c>
       <c r="G5">
-        <v>95.3</v>
+        <v>94.89999999999999</v>
       </c>
       <c r="H5">
-        <v>92.30000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I5">
-        <v>94</v>
+        <v>95.39999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2308,28 +2308,28 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="C6">
-        <v>45.1</v>
+        <v>48.3</v>
       </c>
       <c r="D6">
         <v>28.4</v>
       </c>
       <c r="E6">
-        <v>65.3</v>
+        <v>63.7</v>
       </c>
       <c r="F6">
-        <v>75.2</v>
+        <v>72</v>
       </c>
       <c r="G6">
-        <v>94.39999999999999</v>
+        <v>94.89999999999999</v>
       </c>
       <c r="H6">
-        <v>89.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I6">
-        <v>87.3</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2337,28 +2337,28 @@
         <v>4</v>
       </c>
       <c r="B7">
-        <v>31.5</v>
+        <v>30</v>
       </c>
       <c r="C7">
-        <v>44.5</v>
+        <v>42</v>
       </c>
       <c r="D7">
-        <v>74.59999999999999</v>
+        <v>71.39999999999999</v>
       </c>
       <c r="E7">
-        <v>17.3</v>
+        <v>18.5</v>
       </c>
       <c r="F7">
-        <v>44.9</v>
+        <v>43.3</v>
       </c>
       <c r="G7">
-        <v>49.7</v>
+        <v>50.2</v>
       </c>
       <c r="H7">
-        <v>59.4</v>
+        <v>59.3</v>
       </c>
       <c r="I7">
-        <v>60.9</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2366,28 +2366,28 @@
         <v>0</v>
       </c>
       <c r="B8">
-        <v>58.7</v>
+        <v>60.09999999999999</v>
       </c>
       <c r="C8">
-        <v>32.9</v>
+        <v>31.9</v>
       </c>
       <c r="D8">
-        <v>37.4</v>
+        <v>37.5</v>
       </c>
       <c r="E8">
-        <v>90.10000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="F8">
-        <v>81.5</v>
+        <v>85.39999999999999</v>
       </c>
       <c r="G8">
-        <v>64.5</v>
+        <v>63.7</v>
       </c>
       <c r="H8">
-        <v>57.2</v>
+        <v>54.7</v>
       </c>
       <c r="I8">
-        <v>56.8</v>
+        <v>57.49999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2398,25 +2398,25 @@
         <v>99.90000000000001</v>
       </c>
       <c r="C9">
-        <v>79.5</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="D9">
-        <v>21.8</v>
+        <v>24.9</v>
       </c>
       <c r="E9">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
       <c r="F9">
         <v>11.8</v>
       </c>
       <c r="G9">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="H9">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="I9">
-        <v>3</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2424,28 +2424,28 @@
         <v>3</v>
       </c>
       <c r="B10">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="C10">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="D10">
-        <v>39.90000000000001</v>
+        <v>40</v>
       </c>
       <c r="E10">
-        <v>18.4</v>
+        <v>19.2</v>
       </c>
       <c r="F10">
-        <v>0.7000000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="G10">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H10">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="I10">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2453,13 +2453,13 @@
         <v>2</v>
       </c>
       <c r="B11">
-        <v>44.4</v>
+        <v>46.8</v>
       </c>
       <c r="C11">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="D11">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -2468,7 +2468,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -2868,7 +2868,7 @@
         <v>71</v>
       </c>
       <c r="I2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2888,7 +2888,7 @@
         <v>984.9400000000002</v>
       </c>
       <c r="F3">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -2917,7 +2917,7 @@
         <v>909.46</v>
       </c>
       <c r="F4">
-        <v>97.09999999999999</v>
+        <v>98.3</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -2926,7 +2926,7 @@
         <v>73</v>
       </c>
       <c r="I4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2946,7 +2946,7 @@
         <v>922.1</v>
       </c>
       <c r="F5">
-        <v>94.89999999999999</v>
+        <v>94</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -2975,7 +2975,7 @@
         <v>888.52</v>
       </c>
       <c r="F6">
-        <v>88.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -3004,7 +3004,7 @@
         <v>831.4399999999999</v>
       </c>
       <c r="F7">
-        <v>59.9</v>
+        <v>58.8</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -3033,13 +3033,13 @@
         <v>834.1400000000001</v>
       </c>
       <c r="F8">
-        <v>57.2</v>
+        <v>55.50000000000001</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I8" t="s">
         <v>84</v>
@@ -3065,10 +3065,10 @@
         <v>1.7</v>
       </c>
       <c r="G9">
-        <v>5.3</v>
+        <v>6.3</v>
       </c>
       <c r="H9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I9" t="s">
         <v>85</v>
@@ -3091,13 +3091,13 @@
         <v>739.64</v>
       </c>
       <c r="F10">
-        <v>0.7000000000000001</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="G10">
-        <v>4.100000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="H10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I10" t="s">
         <v>85</v>
@@ -3123,10 +3123,10 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>90.60000000000001</v>
+        <v>90</v>
       </c>
       <c r="H11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I11" t="s">
         <v>86</v>
